--- a/VRPExample/heuristicapproach/src/furgoni.xlsx
+++ b/VRPExample/heuristicapproach/src/furgoni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\OQI_Project\Full Optimizer\VRPExample\heuristicapproach\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98CEDAA-913C-4687-A1D3-1053624AFA49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40238791-30C6-47A2-A2FA-7DFB6301D496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="241">
   <si>
     <t>NUMBER PLATE</t>
   </si>
@@ -481,42 +481,33 @@
     <t>PICKUP</t>
   </si>
   <si>
-    <t xml:space="preserve"> A.DI DEDDA P/C  ENERGI SAVING GROUP </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VIIA G. MARCONI 151 31021 MOGLIANO VENETO TV</t>
+    <t>MARAZZATO GIOVANNI SRL</t>
+  </si>
+  <si>
+    <t>VIA VILLANOVA 35 TREBASELEGHE</t>
+  </si>
+  <si>
+    <t>00:00-23:59</t>
+  </si>
+  <si>
+    <t>MOVISTAR SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VIA OLANDA 5  VIGONZA</t>
+  </si>
+  <si>
+    <t>00:00-12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEMFIS </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LOCALITÀ BATASIOLO 85/A  LA MORRA CUNEO </t>
   </si>
   <si>
     <t>DELIVERY</t>
   </si>
   <si>
-    <t>MARAZZATO GIOVANNI SRL</t>
-  </si>
-  <si>
-    <t>VIA VILLANOVA 35 TREBASELEGHE</t>
-  </si>
-  <si>
-    <t>GUFRAM SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOCALITÀ BATASIOLO 85/A  LA MORRA CUNEO </t>
-  </si>
-  <si>
-    <t>MOVISTAR SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VIA OLANDA 5  VIGONZA</t>
-  </si>
-  <si>
-    <t>00:00-12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEMFIS </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LOCALITÀ BATASIOLO 85/A  LA MORRA CUNEO </t>
-  </si>
-  <si>
     <t xml:space="preserve">SUERMERCATI TOSANO CEREA </t>
   </si>
   <si>
@@ -529,12 +520,6 @@
     <t>VIA SOMMACAMPAGNA 22 VERONA</t>
   </si>
   <si>
-    <t xml:space="preserve">ANDREA ANNA KOFLER </t>
-  </si>
-  <si>
-    <t>VIE DELLE BOCCE 16 NATURNO</t>
-  </si>
-  <si>
     <t xml:space="preserve">IL PIZZICAGNOLO </t>
   </si>
   <si>
@@ -565,24 +550,12 @@
     <t>VIA STAZIONE 113 VALLE LOMELLINA</t>
   </si>
   <si>
-    <t xml:space="preserve">CROSS NECKING </t>
-  </si>
-  <si>
-    <t>VIA LUISA SPAGNOLI 8 MOZZELLANE</t>
-  </si>
-  <si>
     <t>MARCONI</t>
   </si>
   <si>
     <t>VIA 11 SETTEMBRE 2001 VOLGARGNE</t>
   </si>
   <si>
-    <t xml:space="preserve">MARCO SALVI </t>
-  </si>
-  <si>
-    <t>VIA VEZZANI 175 GENOVA</t>
-  </si>
-  <si>
     <t>DABRAZZI PACKAGING</t>
   </si>
   <si>
@@ -592,12 +565,6 @@
     <t>08:00-17:30</t>
   </si>
   <si>
-    <t>GEODIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIA DOGANA PO' 15 CASTEL SAN GIOVANNI </t>
-  </si>
-  <si>
     <t>AGRIACRO TECH SRL</t>
   </si>
   <si>
@@ -631,12 +598,6 @@
     <t xml:space="preserve">PICKUP </t>
   </si>
   <si>
-    <t>PENTAGON FREIGHT SERVICES ITALIA SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIA AURELIO NICOLODI 15 </t>
-  </si>
-  <si>
     <t>I.B.O. SRL</t>
   </si>
   <si>
@@ -697,24 +658,12 @@
     <t xml:space="preserve">VIA NUOVA PONENTE 29 CARPI </t>
   </si>
   <si>
-    <t>GAUDì TRADE SPA ROLO</t>
-  </si>
-  <si>
-    <t>VIA VINCENZO MARI 7 ROLO</t>
-  </si>
-  <si>
     <t>C/O MTC PROREO SRL</t>
   </si>
   <si>
     <t>STRADA PEDEMONTANA EST 27 TRAVERSETOLO</t>
   </si>
   <si>
-    <t xml:space="preserve">VECTOR SPA </t>
-  </si>
-  <si>
-    <t>VIA REDIPUGLIA 7 CASTELLANZA</t>
-  </si>
-  <si>
     <t>AREA FOOD GASTRONOMIA CASTELFRUTTA SRL</t>
   </si>
   <si>
@@ -727,15 +676,6 @@
     <t>VIA DIVISIONE JULIA 23 MERETO DI TOMBA</t>
   </si>
   <si>
-    <t>IVAS WAREHOUSING SRL</t>
-  </si>
-  <si>
-    <t>SP 161 46  VIGNATE</t>
-  </si>
-  <si>
-    <t>08:30-17:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">DIPHARMA FRANCIS SRL </t>
   </si>
   <si>
@@ -775,12 +715,6 @@
     <t xml:space="preserve">PIAZZALE ORMIG REGIONE CARLOVI 12A  OVADA ALTA </t>
   </si>
   <si>
-    <t>IMEB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIA CIRCONVALLAZIONE 124 ACQUI TERME </t>
-  </si>
-  <si>
     <t>C.TO CLIENTE IMEB</t>
   </si>
   <si>
@@ -799,6 +733,9 @@
     <t>VIALE CASSALA 40 MILANO</t>
   </si>
   <si>
+    <t>09:00-23:59</t>
+  </si>
+  <si>
     <t>STEROID SPA</t>
   </si>
   <si>
@@ -821,19 +758,13 @@
   </si>
   <si>
     <t xml:space="preserve">VIA ALBINONI 50 SOLIERA </t>
-  </si>
-  <si>
-    <t>00:00-23:59</t>
-  </si>
-  <si>
-    <t>09:00-23:59</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -850,7 +781,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -869,13 +800,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -988,6 +912,9 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1000,7 +927,7 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1015,7 +942,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1033,7 +960,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1048,29 +975,30 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1376,22 +1304,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:O146"/>
+  <dimension ref="A1:O135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="53.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="62.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="62.28515625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="62.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.42578125" style="35" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" style="35" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="43.28515625" style="36" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.7109375" style="35" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="8" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1403,48 +1329,48 @@
       <c r="B1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="1" t="s">
         <v>131</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>133</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>135</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="L1" s="28" t="s">
+      <c r="L1" s="13" t="s">
         <v>121</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="18.75" customHeight="1">
+    <row r="2" spans="1:15" ht="19.5" customHeight="1">
       <c r="A2" s="29" t="s">
         <v>139</v>
       </c>
       <c r="B2" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="29">
         <v>15069</v>
       </c>
       <c r="D2" s="29" t="s">
@@ -1471,23 +1397,23 @@
       <c r="K2" s="30">
         <v>6</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="19" t="s">
         <v>126</v>
       </c>
       <c r="M2" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-    </row>
-    <row r="3" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A3" s="18" t="s">
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A3" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="19">
         <v>20881</v>
       </c>
       <c r="D3" s="29" t="s">
@@ -1502,90 +1428,90 @@
       <c r="G3" s="30">
         <v>30</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="15">
         <v>500</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="16">
         <f>445*115*270/1000000</f>
         <v>13.81725</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="15">
         <v>2</v>
       </c>
-      <c r="L3" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-    </row>
-    <row r="4" spans="1:15" ht="18.75" customHeight="1">
+      <c r="L3" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+    </row>
+    <row r="4" spans="1:15" ht="19.5" customHeight="1">
       <c r="A4" s="29" t="s">
         <v>148</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="30">
-        <v>31021</v>
+      <c r="C4" s="29">
+        <v>35010</v>
       </c>
       <c r="D4" s="29" t="s">
         <v>141</v>
       </c>
       <c r="E4" s="30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>262</v>
+        <v>150</v>
       </c>
       <c r="G4" s="30">
         <v>30</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I4" s="30">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="J4" s="31">
-        <f>445*115*270/1000000</f>
-        <v>13.81725</v>
+        <f>80*120*100/1000000</f>
+        <v>0.96</v>
       </c>
       <c r="K4" s="30">
-        <v>2</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-    </row>
-    <row r="5" spans="1:15" ht="18.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1">
       <c r="A5" s="29" t="s">
         <v>151</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>35010</v>
       </c>
       <c r="D5" s="29" t="s">
         <v>141</v>
       </c>
       <c r="E5" s="30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>262</v>
+        <v>153</v>
       </c>
       <c r="G5" s="30">
         <v>30</v>
@@ -1594,1472 +1520,1467 @@
         <v>147</v>
       </c>
       <c r="I5" s="30">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J5" s="31">
-        <f>80*120*100/1000000</f>
-        <v>0.96</v>
+        <f>120*115*120/1000000</f>
+        <v>1.6559999999999999</v>
       </c>
       <c r="K5" s="30">
         <v>1</v>
       </c>
-      <c r="L5" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-    </row>
-    <row r="6" spans="1:15" ht="18.75" customHeight="1">
+      <c r="L5" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" customHeight="1">
       <c r="A6" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="30">
+        <v>155</v>
+      </c>
+      <c r="C6" s="29">
         <v>12064</v>
       </c>
       <c r="D6" s="29" t="s">
         <v>141</v>
       </c>
       <c r="E6" s="30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>262</v>
+        <v>153</v>
       </c>
       <c r="G6" s="30">
         <v>30</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I6" s="30">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J6" s="31">
-        <f>80*120*100/1000000</f>
-        <v>0.96</v>
+        <f>120*115*120/1000000</f>
+        <v>1.6559999999999999</v>
       </c>
       <c r="K6" s="30">
         <v>1</v>
       </c>
-      <c r="L6" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M6" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-    </row>
-    <row r="7" spans="1:15" ht="18.75" customHeight="1">
+      <c r="L6" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+    </row>
+    <row r="7" spans="1:15" ht="19.5" customHeight="1">
       <c r="A7" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="C7" s="30">
-        <v>35010</v>
+        <v>157</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="19">
+        <v>37053</v>
       </c>
       <c r="D7" s="29" t="s">
         <v>141</v>
       </c>
       <c r="E7" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G7" s="30">
         <v>30</v>
       </c>
       <c r="H7" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="I7" s="30">
+        <v>600</v>
+      </c>
+      <c r="J7" s="31">
+        <f>5*100*120*80/1000000</f>
+        <v>4.8</v>
+      </c>
+      <c r="K7" s="30">
+        <v>5</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="N7" s="19"/>
+    </row>
+    <row r="8" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A8" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="29">
+        <v>37137</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" s="30">
+        <v>0</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="30">
+        <v>30</v>
+      </c>
+      <c r="H8" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="I7" s="30">
-        <v>60</v>
-      </c>
-      <c r="J7" s="31">
+      <c r="I8" s="30">
+        <v>104</v>
+      </c>
+      <c r="J8" s="31">
+        <f>((134*17*17)+(250*25*24)+(237*23*31)+(144*36*24))/1000000</f>
+        <v>0.48212300000000002</v>
+      </c>
+      <c r="K8" s="30">
+        <v>4</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+    </row>
+    <row r="9" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A9" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="29">
+        <v>38017</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" s="30">
+        <v>0</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G9" s="30">
+        <v>30</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="I9" s="30">
+        <v>400</v>
+      </c>
+      <c r="J9" s="31">
+        <f>4*100*80*120/1000000</f>
+        <v>3.84</v>
+      </c>
+      <c r="K9" s="30">
+        <v>4</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+    </row>
+    <row r="10" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A10" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="29">
+        <v>39055</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="30">
+        <v>0</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="G10" s="30">
+        <v>30</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="I10" s="30">
+        <v>1200</v>
+      </c>
+      <c r="J10" s="31">
+        <f>12*100*80*120/1000000</f>
+        <v>11.52</v>
+      </c>
+      <c r="K10" s="30">
+        <v>12</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+    </row>
+    <row r="11" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A11" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" s="29">
+        <v>13320</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="30">
+        <v>4</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G11" s="30">
+        <v>30</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="I11" s="30">
+        <v>4201</v>
+      </c>
+      <c r="J11" s="31">
+        <f>10*100*80*120/1000000</f>
+        <v>9.6</v>
+      </c>
+      <c r="K11" s="30">
+        <v>10</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+    </row>
+    <row r="12" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A12" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="29">
+        <v>27020</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="30">
+        <v>0</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="30">
+        <v>30</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="I12" s="30">
+        <v>25100</v>
+      </c>
+      <c r="J12" s="31">
+        <f>33*100*80*120/1000000</f>
+        <v>31.68</v>
+      </c>
+      <c r="K12" s="30">
+        <v>33</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A13" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="29">
+        <v>37020</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="30">
+        <v>0</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" s="30">
+        <v>30</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="I13" s="30">
+        <v>6000</v>
+      </c>
+      <c r="J13" s="30">
+        <f>(4*(120*100*100)+(150*80*100))/1000000</f>
+        <v>6</v>
+      </c>
+      <c r="K13" s="30">
+        <v>5</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A14" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14" s="29">
+        <v>25030</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="30">
+        <v>0</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="G14" s="30">
+        <v>30</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="I14" s="31">
+        <v>6675.74</v>
+      </c>
+      <c r="J14" s="31">
+        <f>(9*(100*120*160)+ 4*(100*120*130))/1000000</f>
+        <v>23.52</v>
+      </c>
+      <c r="K14" s="30">
+        <v>13</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A15" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="29">
+        <v>18026</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" s="30">
+        <v>0</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="G15" s="30">
+        <v>30</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="30">
+        <v>850</v>
+      </c>
+      <c r="J15" s="31">
+        <v>26.63</v>
+      </c>
+      <c r="K15" s="30">
+        <v>6</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A16" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="29">
+        <v>10042</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" s="30">
+        <v>0</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="G16" s="30">
+        <v>30</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="I16" s="31">
+        <v>74.010000000000005</v>
+      </c>
+      <c r="J16" s="31">
+        <f>120*80*11/1000000</f>
+        <v>0.1056</v>
+      </c>
+      <c r="K16" s="30">
+        <v>1</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A17" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" s="29">
+        <v>25126</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="30">
+        <v>0</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="G17" s="30">
+        <v>30</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="I17" s="30">
+        <v>598</v>
+      </c>
+      <c r="J17" s="16">
         <f>120*115*120/1000000</f>
         <v>1.6559999999999999</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K17" s="30">
         <v>1</v>
       </c>
-      <c r="L7" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M7" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-    </row>
-    <row r="8" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A8" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="30">
-        <v>12064</v>
-      </c>
-      <c r="D8" s="29" t="s">
+      <c r="L17" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A18" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="29">
+        <v>20884</v>
+      </c>
+      <c r="D18" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E18" s="30">
+        <v>0</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="G18" s="30">
+        <v>30</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I18" s="30">
+        <v>2400</v>
+      </c>
+      <c r="J18" s="31">
+        <f>4*100*120*100/1000000</f>
+        <v>4.8</v>
+      </c>
+      <c r="K18" s="30">
+        <v>4</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A19" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C19" s="29">
+        <v>28015</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="30">
+        <v>0</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" s="30">
+        <v>30</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="I19" s="30">
+        <v>486</v>
+      </c>
+      <c r="J19" s="16">
+        <f>100*80*120/1000000</f>
+        <v>0.96</v>
+      </c>
+      <c r="K19" s="30">
         <v>1</v>
       </c>
-      <c r="F8" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="G8" s="30">
+      <c r="L19" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A20" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="29">
+        <v>28053</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" s="30">
+        <v>0</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" s="30">
         <v>30</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="H20" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" s="30">
+        <v>25</v>
+      </c>
+      <c r="J20" s="16">
+        <f>2*60*20*50/1000000</f>
+        <v>0.12</v>
+      </c>
+      <c r="K20" s="30">
+        <v>2</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A21" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="29">
+        <v>28046</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="30">
+        <v>0</v>
+      </c>
+      <c r="F21" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="I8" s="30">
-        <v>60</v>
-      </c>
-      <c r="J8" s="31">
-        <f>120*115*120/1000000</f>
-        <v>1.6559999999999999</v>
-      </c>
-      <c r="K8" s="30">
+      <c r="G21" s="30">
+        <v>30</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="I21" s="30">
+        <v>6000</v>
+      </c>
+      <c r="J21" s="16">
+        <f>6*120*115*120/1000000</f>
+        <v>9.9359999999999999</v>
+      </c>
+      <c r="K21" s="30">
+        <v>6</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A22" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="29">
+        <v>20129</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="30">
+        <v>0</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G22" s="30">
+        <v>30</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I22" s="15">
+        <v>600</v>
+      </c>
+      <c r="J22" s="31">
+        <f>6*100*80*120/1000000</f>
+        <v>5.76</v>
+      </c>
+      <c r="K22" s="30">
+        <v>6</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A23" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="29">
+        <v>16043</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" s="30">
+        <v>0</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="30">
+        <v>30</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="15">
+        <v>600</v>
+      </c>
+      <c r="J23" s="31">
+        <f>6*100*80*120/1000000</f>
+        <v>5.76</v>
+      </c>
+      <c r="K23" s="30">
+        <v>6</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M23" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A24" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" s="29">
+        <v>60021</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" s="30">
+        <v>0</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="30">
+        <v>30</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="I24" s="15">
+        <v>150</v>
+      </c>
+      <c r="J24" s="31">
+        <f>2*100*80*120/1000000</f>
+        <v>1.92</v>
+      </c>
+      <c r="K24" s="30">
+        <v>2</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A25" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25" s="29">
+        <v>47895</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="E25" s="30">
+        <v>0</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="G25" s="30">
+        <v>30</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I25" s="30">
+        <v>520</v>
+      </c>
+      <c r="J25" s="31">
+        <f>(3*(80*120*160)+(80*120*60))/1000000</f>
+        <v>5.1840000000000002</v>
+      </c>
+      <c r="K25" s="30">
+        <v>4</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="M25" s="29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A26" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="C26" s="29">
+        <v>28061</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" s="30">
+        <v>0</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" s="30">
+        <v>30</v>
+      </c>
+      <c r="H26" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="I26" s="30">
+        <v>584</v>
+      </c>
+      <c r="J26" s="31">
+        <f>100*80*120/1000000</f>
+        <v>0.96</v>
+      </c>
+      <c r="K26" s="30">
         <v>1</v>
       </c>
-      <c r="L8" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M8" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-    </row>
-    <row r="9" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A9" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C9" s="14">
-        <v>37053</v>
-      </c>
-      <c r="D9" s="29" t="s">
+      <c r="L26" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A27" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" s="29">
+        <v>41012</v>
+      </c>
+      <c r="D27" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E27" s="30">
         <v>0</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G9" s="30">
+      <c r="F27" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" s="30">
         <v>30</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H27" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I27" s="31">
+        <v>517.86</v>
+      </c>
+      <c r="J27" s="31">
+        <v>2.95</v>
+      </c>
+      <c r="K27" s="15">
+        <v>1</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M27" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A28" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="29">
+        <v>43029</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E28" s="30">
+        <v>0</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G28" s="30">
+        <v>30</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I28" s="30">
+        <v>2719</v>
+      </c>
+      <c r="J28" s="31">
+        <v>7.6020000000000003</v>
+      </c>
+      <c r="K28" s="30">
+        <v>10</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="M28" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A29" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="B29" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" s="29">
+        <v>34126</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29" s="30">
+        <v>0</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G29" s="30">
+        <v>30</v>
+      </c>
+      <c r="H29" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="I9" s="30">
-        <v>600</v>
-      </c>
-      <c r="J9" s="31">
+      <c r="I29" s="30">
+        <v>10000</v>
+      </c>
+      <c r="J29" s="30">
+        <v>12</v>
+      </c>
+      <c r="K29" s="30">
+        <v>15</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M29" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A30" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="B30" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="C30" s="29">
+        <v>33036</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="30">
+        <v>0</v>
+      </c>
+      <c r="F30" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G30" s="30">
+        <v>30</v>
+      </c>
+      <c r="H30" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I30" s="30">
+        <v>1328</v>
+      </c>
+      <c r="J30" s="16">
+        <f>(9*(100*120*160)+ 4*(100*120*130))/1000000</f>
+        <v>23.52</v>
+      </c>
+      <c r="K30" s="30">
+        <v>8</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A31" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="29">
+        <v>33036</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="30">
+        <v>0</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G31" s="30">
+        <v>30</v>
+      </c>
+      <c r="H31" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I31" s="30">
+        <v>10</v>
+      </c>
+      <c r="J31" s="31">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="K31" s="30">
+        <v>1</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M31" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A32" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="B32" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" s="29">
+        <v>12100</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="30">
+        <v>0</v>
+      </c>
+      <c r="F32" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G32" s="30">
+        <v>30</v>
+      </c>
+      <c r="H32" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="I32" s="30">
+        <v>2447</v>
+      </c>
+      <c r="J32" s="16">
+        <f>(9*(100*120*160)+ 4*(100*120*130))/1000000</f>
+        <v>23.52</v>
+      </c>
+      <c r="K32" s="30">
+        <v>6</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M32" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A33" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="29">
+        <v>14040</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="30">
+        <v>0</v>
+      </c>
+      <c r="F33" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="G33" s="30">
+        <v>30</v>
+      </c>
+      <c r="H33" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I33" s="30">
+        <v>1000</v>
+      </c>
+      <c r="J33" s="16">
+        <f>2.06*2.3*4.6</f>
+        <v>21.794799999999995</v>
+      </c>
+      <c r="K33" s="15">
+        <v>10</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M33" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A34" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="B34" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="C34" s="29">
+        <v>10040</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="30">
+        <v>0</v>
+      </c>
+      <c r="F34" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G34" s="30">
+        <v>30</v>
+      </c>
+      <c r="H34" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="I34" s="16">
+        <v>6675.74</v>
+      </c>
+      <c r="J34" s="16">
+        <f>(9*(100*120*160)+ 4*(100*120*130))/1000000</f>
+        <v>23.52</v>
+      </c>
+      <c r="K34" s="30">
+        <v>13</v>
+      </c>
+      <c r="L34" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A35" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="29">
+        <v>10020</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="30">
+        <v>0</v>
+      </c>
+      <c r="F35" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G35" s="30">
+        <v>30</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="I35" s="15">
+        <v>486</v>
+      </c>
+      <c r="J35" s="16">
+        <f>100*80*120/1000000</f>
+        <v>0.96</v>
+      </c>
+      <c r="K35" s="30">
+        <v>1</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M35" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A36" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="B36" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="C36" s="29">
+        <v>15076</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="30">
+        <v>0</v>
+      </c>
+      <c r="F36" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G36" s="30">
+        <v>30</v>
+      </c>
+      <c r="H36" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="I36" s="30">
+        <v>4053</v>
+      </c>
+      <c r="J36" s="31">
+        <v>1.54</v>
+      </c>
+      <c r="K36" s="30">
+        <v>2</v>
+      </c>
+      <c r="L36" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M36" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A37" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="C37" s="29">
+        <v>33043</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37" s="30">
+        <v>1</v>
+      </c>
+      <c r="F37" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G37" s="30">
+        <v>30</v>
+      </c>
+      <c r="H37" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="I37" s="30">
+        <f>4*600+400</f>
+        <v>2800</v>
+      </c>
+      <c r="J37" s="16">
         <f>5*100*120*80/1000000</f>
         <v>4.8</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K37" s="30">
         <v>5</v>
       </c>
-      <c r="L9" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N9" s="18"/>
-    </row>
-    <row r="10" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A10" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" s="30">
-        <v>37137</v>
-      </c>
-      <c r="D10" s="29" t="s">
+      <c r="L37" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M37" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A38" s="29" t="s">
+        <v>228</v>
+      </c>
+      <c r="B38" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C38" s="29">
+        <v>20044</v>
+      </c>
+      <c r="D38" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E38" s="30">
         <v>0</v>
       </c>
-      <c r="F10" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G10" s="30">
+      <c r="F38" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G38" s="30">
         <v>30</v>
       </c>
-      <c r="H10" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="I10" s="30">
-        <v>104</v>
-      </c>
-      <c r="J10" s="31">
-        <f>((134*17*17)+(250*25*24)+(237*23*31)+(144*36*24))/1000000</f>
-        <v>0.48212300000000002</v>
-      </c>
-      <c r="K10" s="30">
-        <v>4</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M10" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-    </row>
-    <row r="11" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A11" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="30">
-        <v>21056</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E11" s="30">
-        <v>0</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G11" s="30">
-        <v>30</v>
-      </c>
-      <c r="H11" s="29" t="s">
+      <c r="H38" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="I11" s="30">
-        <v>104</v>
-      </c>
-      <c r="J11" s="31">
-        <f>((134*17*17)+(250*25*24)+(237*23*31)+(144*36*24))/1000000</f>
-        <v>0.48212300000000002</v>
-      </c>
-      <c r="K11" s="30">
-        <v>4</v>
-      </c>
-      <c r="L11" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-    </row>
-    <row r="12" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A12" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="C12" s="30">
-        <v>38017</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12" s="30">
-        <v>0</v>
-      </c>
-      <c r="F12" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G12" s="30">
-        <v>30</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I12" s="30">
-        <v>400</v>
-      </c>
-      <c r="J12" s="31">
-        <f>4*100*80*120/1000000</f>
-        <v>3.84</v>
-      </c>
-      <c r="K12" s="30">
-        <v>4</v>
-      </c>
-      <c r="L12" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M12" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-    </row>
-    <row r="13" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A13" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="30">
-        <v>39055</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E13" s="30">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="G13" s="30">
-        <v>30</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="I13" s="30">
-        <v>1200</v>
-      </c>
-      <c r="J13" s="31">
-        <f>12*100*80*120/1000000</f>
-        <v>11.52</v>
-      </c>
-      <c r="K13" s="30">
-        <v>12</v>
-      </c>
-      <c r="L13" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M13" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-    </row>
-    <row r="14" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A14" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="C14" s="30">
-        <v>13320</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="E14" s="30">
-        <v>4</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G14" s="30">
-        <v>30</v>
-      </c>
-      <c r="H14" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I14" s="30">
-        <v>4201</v>
-      </c>
-      <c r="J14" s="31">
-        <f>10*100*80*120/1000000</f>
-        <v>9.6</v>
-      </c>
-      <c r="K14" s="30">
-        <v>10</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M14" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-    </row>
-    <row r="15" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A15" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="30">
-        <v>27020</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15" s="30">
-        <v>0</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G15" s="30">
-        <v>30</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="I15" s="30">
-        <v>25100</v>
-      </c>
-      <c r="J15" s="31">
-        <f>33*100*80*120/1000000</f>
-        <v>31.68</v>
-      </c>
-      <c r="K15" s="30">
-        <v>33</v>
-      </c>
-      <c r="L15" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M15" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A16" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="30">
-        <v>37060</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" s="30">
-        <v>0</v>
-      </c>
-      <c r="F16" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G16" s="30">
-        <v>30</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I16" s="30">
-        <v>25100</v>
-      </c>
-      <c r="J16" s="31">
-        <f>33*100*80*120/1000000</f>
-        <v>31.68</v>
-      </c>
-      <c r="K16" s="30">
-        <v>33</v>
-      </c>
-      <c r="L16" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M16" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A17" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="C17" s="30">
-        <v>37020</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" s="30">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G17" s="30">
-        <v>30</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="I17" s="30">
-        <v>6000</v>
-      </c>
-      <c r="J17" s="30">
-        <f>(4*(120*100*100)+(150*80*100))/1000000</f>
-        <v>6</v>
-      </c>
-      <c r="K17" s="30">
-        <v>5</v>
-      </c>
-      <c r="L17" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M17" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A18" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="C18" s="30">
-        <v>16159</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E18" s="30">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G18" s="30">
-        <v>30</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I18" s="30">
-        <v>6000</v>
-      </c>
-      <c r="J18" s="30">
-        <f>(4*(120*100*100) +(150*80*100))/1000000</f>
-        <v>6</v>
-      </c>
-      <c r="K18" s="30">
-        <v>5</v>
-      </c>
-      <c r="L18" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M18" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A19" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="30">
-        <v>25030</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" s="30">
-        <v>0</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="G19" s="30">
-        <v>30</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="I19" s="31">
+      <c r="I38" s="16">
         <v>6675.74</v>
       </c>
-      <c r="J19" s="31">
+      <c r="J38" s="16">
         <f>(9*(100*120*160)+ 4*(100*120*130))/1000000</f>
         <v>23.52</v>
       </c>
-      <c r="K19" s="30">
+      <c r="K38" s="30">
         <v>13</v>
       </c>
-      <c r="L19" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M19" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="C20" s="30">
-        <v>29015</v>
-      </c>
-      <c r="D20" s="29" t="s">
+      <c r="L38" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M38" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A39" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="C39" s="29">
+        <v>20143</v>
+      </c>
+      <c r="D39" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E39" s="30">
         <v>0</v>
       </c>
-      <c r="F20" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="G20" s="30">
+      <c r="F39" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="G39" s="30">
         <v>30</v>
       </c>
-      <c r="H20" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I20" s="31">
-        <v>6675.74</v>
-      </c>
-      <c r="J20" s="31">
-        <f>(9*(100*120*160)+4*(100*120*130))/1000000</f>
-        <v>23.52</v>
-      </c>
-      <c r="K20" s="30">
-        <v>13</v>
-      </c>
-      <c r="L20" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M20" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="C21" s="30">
-        <v>18026</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" s="30">
-        <v>0</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="G21" s="30">
-        <v>30</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I21" s="30">
-        <v>850</v>
-      </c>
-      <c r="J21" s="31">
-        <v>26.63</v>
-      </c>
-      <c r="K21" s="30">
-        <v>6</v>
-      </c>
-      <c r="L21" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M21" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="C22" s="30">
-        <v>10042</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" s="30">
-        <v>0</v>
-      </c>
-      <c r="F22" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="G22" s="30">
-        <v>30</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="I22" s="31">
-        <v>74.010000000000005</v>
-      </c>
-      <c r="J22" s="31">
-        <f>120*80*11/1000000</f>
-        <v>0.1056</v>
-      </c>
-      <c r="K22" s="30">
-        <v>1</v>
-      </c>
-      <c r="L22" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M22" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A23" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" s="30">
-        <v>25126</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" s="30">
-        <v>0</v>
-      </c>
-      <c r="F23" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="G23" s="30">
-        <v>30</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I23" s="30">
-        <v>598</v>
-      </c>
-      <c r="J23" s="15">
-        <f>120*115*120/1000000</f>
-        <v>1.6559999999999999</v>
-      </c>
-      <c r="K23" s="30">
-        <v>1</v>
-      </c>
-      <c r="L23" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M23" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="C24" s="30">
-        <v>20884</v>
-      </c>
-      <c r="D24" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E24" s="30">
-        <v>0</v>
-      </c>
-      <c r="F24" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="G24" s="30">
-        <v>30</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="I24" s="30">
-        <v>2400</v>
-      </c>
-      <c r="J24" s="31">
-        <f>4*100*120*100/1000000</f>
-        <v>4.8</v>
-      </c>
-      <c r="K24" s="30">
-        <v>4</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M24" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C25" s="30">
-        <v>20161</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E25" s="30">
-        <v>0</v>
-      </c>
-      <c r="F25" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G25" s="30">
-        <v>30</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I25" s="30">
-        <v>2400</v>
-      </c>
-      <c r="J25" s="31">
-        <f>4*100*120*100/1000000</f>
-        <v>4.8</v>
-      </c>
-      <c r="K25" s="30">
-        <v>4</v>
-      </c>
-      <c r="L25" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M25" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="B26" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="C26" s="30">
-        <v>28015</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E26" s="30">
-        <v>0</v>
-      </c>
-      <c r="F26" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G26" s="30">
-        <v>30</v>
-      </c>
-      <c r="H26" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I26" s="30">
-        <v>486</v>
-      </c>
-      <c r="J26" s="15">
+      <c r="H39" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="I39" s="30">
+        <v>3400</v>
+      </c>
+      <c r="J39" s="16">
         <f>100*80*120/1000000</f>
         <v>0.96</v>
       </c>
-      <c r="K26" s="30">
+      <c r="K39" s="30">
         <v>1</v>
       </c>
-      <c r="L26" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M26" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="C27" s="30">
-        <v>28053</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E27" s="30">
-        <v>0</v>
-      </c>
-      <c r="F27" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G27" s="30">
-        <v>30</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I27" s="30">
-        <v>25</v>
-      </c>
-      <c r="J27" s="15">
-        <f>2*60*20*50/1000000</f>
-        <v>0.12</v>
-      </c>
-      <c r="K27" s="30">
-        <v>2</v>
-      </c>
-      <c r="L27" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="M27" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="B28" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="C28" s="30">
-        <v>28046</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" s="30">
-        <v>0</v>
-      </c>
-      <c r="F28" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G28" s="30">
-        <v>30</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I28" s="30">
-        <v>6000</v>
-      </c>
-      <c r="J28" s="15">
-        <f>6*120*115*120/1000000</f>
-        <v>9.9359999999999999</v>
-      </c>
-      <c r="K28" s="30">
-        <v>6</v>
-      </c>
-      <c r="L28" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M28" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="B29" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C29" s="30">
-        <v>20129</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E29" s="30">
-        <v>0</v>
-      </c>
-      <c r="F29" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G29" s="30">
-        <v>30</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="I29" s="14">
-        <v>600</v>
-      </c>
-      <c r="J29" s="31">
-        <f>6*100*80*120/1000000</f>
-        <v>5.76</v>
-      </c>
-      <c r="K29" s="30">
-        <v>6</v>
-      </c>
-      <c r="L29" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M29" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="B30" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C30" s="30">
-        <v>16043</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" s="30">
-        <v>0</v>
-      </c>
-      <c r="F30" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G30" s="30">
-        <v>30</v>
-      </c>
-      <c r="H30" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I30" s="14">
-        <v>600</v>
-      </c>
-      <c r="J30" s="31">
-        <f>6*100*80*120/1000000</f>
-        <v>5.76</v>
-      </c>
-      <c r="K30" s="30">
-        <v>6</v>
-      </c>
-      <c r="L30" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M30" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="B31" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="C31" s="30">
-        <v>60021</v>
-      </c>
-      <c r="D31" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" s="30">
-        <v>0</v>
-      </c>
-      <c r="F31" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G31" s="30">
-        <v>30</v>
-      </c>
-      <c r="H31" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I31" s="14">
-        <v>150</v>
-      </c>
-      <c r="J31" s="31">
-        <f>2*100*80*120/1000000</f>
-        <v>1.92</v>
-      </c>
-      <c r="K31" s="30">
-        <v>2</v>
-      </c>
-      <c r="L31" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M31" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="B32" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="C32" s="30">
-        <v>47895</v>
-      </c>
-      <c r="D32" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="E32" s="30">
-        <v>0</v>
-      </c>
-      <c r="F32" s="29" t="s">
-        <v>215</v>
-      </c>
-      <c r="G32" s="30">
-        <v>30</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="I32" s="30">
-        <v>520</v>
-      </c>
-      <c r="J32" s="31">
-        <f>(3*(80*120*160)+(80*120*60))/1000000</f>
-        <v>5.1840000000000002</v>
-      </c>
-      <c r="K32" s="30">
-        <v>4</v>
-      </c>
-      <c r="L32" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="M32" s="29" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>216</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="C33" s="30">
-        <v>28061</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" s="30">
-        <v>0</v>
-      </c>
-      <c r="F33" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G33" s="30">
-        <v>30</v>
-      </c>
-      <c r="H33" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I33" s="30">
-        <v>584</v>
-      </c>
-      <c r="J33" s="31">
-        <f>100*80*120/1000000</f>
-        <v>0.96</v>
-      </c>
-      <c r="K33" s="30">
-        <v>1</v>
-      </c>
-      <c r="L33" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M33" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="B34" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="C34" s="30">
-        <v>41012</v>
-      </c>
-      <c r="D34" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" s="30">
-        <v>0</v>
-      </c>
-      <c r="F34" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G34" s="30">
-        <v>30</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="I34" s="31">
-        <v>517.86</v>
-      </c>
-      <c r="J34" s="31">
-        <v>2.95</v>
-      </c>
-      <c r="K34" s="14">
-        <v>1</v>
-      </c>
-      <c r="L34" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M34" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="B35" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="C35" s="30">
-        <v>42030</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E35" s="30">
-        <v>1</v>
-      </c>
-      <c r="F35" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G35" s="30">
-        <v>30</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I35" s="31">
-        <v>517.86</v>
-      </c>
-      <c r="J35" s="31">
-        <v>2.95</v>
-      </c>
-      <c r="K35" s="14">
-        <v>1</v>
-      </c>
-      <c r="L35" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M35" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A36" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="B36" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="C36" s="30">
-        <v>43029</v>
-      </c>
-      <c r="D36" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" s="30">
-        <v>0</v>
-      </c>
-      <c r="F36" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G36" s="30">
-        <v>30</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="I36" s="30">
-        <v>2719</v>
-      </c>
-      <c r="J36" s="31">
-        <v>7.6020000000000003</v>
-      </c>
-      <c r="K36" s="30">
-        <v>10</v>
-      </c>
-      <c r="L36" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="M36" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="B37" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="C37" s="30">
-        <v>21053</v>
-      </c>
-      <c r="D37" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E37" s="30">
-        <v>0</v>
-      </c>
-      <c r="F37" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G37" s="30">
-        <v>30</v>
-      </c>
-      <c r="H37" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I37" s="30">
-        <v>2719</v>
-      </c>
-      <c r="J37" s="31">
-        <v>7.6020000000000003</v>
-      </c>
-      <c r="K37" s="30">
-        <v>10</v>
-      </c>
-      <c r="L37" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="M37" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A38" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="B38" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="C38" s="30">
-        <v>34126</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E38" s="30">
-        <v>0</v>
-      </c>
-      <c r="F38" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G38" s="30">
-        <v>30</v>
-      </c>
-      <c r="H38" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I38" s="30">
-        <v>10000</v>
-      </c>
-      <c r="J38" s="30">
-        <v>12</v>
-      </c>
-      <c r="K38" s="30">
-        <v>15</v>
-      </c>
-      <c r="L38" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M38" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A39" s="29" t="s">
-        <v>228</v>
-      </c>
-      <c r="B39" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="C39" s="30">
-        <v>33036</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" s="30">
-        <v>0</v>
-      </c>
-      <c r="F39" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G39" s="30">
-        <v>30</v>
-      </c>
-      <c r="H39" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="I39" s="30">
-        <v>1328</v>
-      </c>
-      <c r="J39" s="15">
-        <f>(9*(100*120*160)+ 4*(100*120*130))/1000000</f>
-        <v>23.52</v>
-      </c>
-      <c r="K39" s="30">
-        <v>8</v>
-      </c>
-      <c r="L39" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="M39" s="18" t="s">
+      <c r="L39" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="M39" s="19" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="18.75" customHeight="1">
       <c r="A40" s="29" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B40" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="30">
-        <v>20052</v>
+        <v>234</v>
+      </c>
+      <c r="C40" s="29">
+        <v>20093</v>
       </c>
       <c r="D40" s="29" t="s">
         <v>141</v>
@@ -3068,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="G40" s="30">
         <v>30</v>
@@ -3077,31 +2998,31 @@
         <v>143</v>
       </c>
       <c r="I40" s="30">
-        <v>1328</v>
-      </c>
-      <c r="J40" s="15">
-        <f>(9*(100*120*160)+ 4*(100*120*130))/1000000</f>
-        <v>23.52</v>
+        <v>5064</v>
+      </c>
+      <c r="J40" s="16">
+        <f>3*100*80*120/1000000</f>
+        <v>2.88</v>
       </c>
       <c r="K40" s="30">
-        <v>8</v>
-      </c>
-      <c r="L40" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="M40" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="L40" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="M40" s="19" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="18.75" customHeight="1">
       <c r="A41" s="29" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B41" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="C41" s="30">
-        <v>33036</v>
+        <v>236</v>
+      </c>
+      <c r="C41" s="29">
+        <v>21050</v>
       </c>
       <c r="D41" s="29" t="s">
         <v>141</v>
@@ -3110,81 +3031,82 @@
         <v>0</v>
       </c>
       <c r="F41" s="29" t="s">
-        <v>262</v>
+        <v>202</v>
       </c>
       <c r="G41" s="30">
         <v>30</v>
       </c>
       <c r="H41" s="29" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="I41" s="30">
-        <v>10</v>
+        <v>298</v>
       </c>
       <c r="J41" s="31">
-        <v>1.7999999999999999E-2</v>
+        <f>100*120*160/1000000</f>
+        <v>1.92</v>
       </c>
       <c r="K41" s="30">
         <v>1</v>
       </c>
-      <c r="L41" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M41" s="18" t="s">
+      <c r="L41" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="M41" s="19" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="18.75" customHeight="1">
       <c r="A42" s="29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="C42" s="30">
-        <v>12100</v>
+        <v>238</v>
+      </c>
+      <c r="C42" s="29">
+        <v>20060</v>
       </c>
       <c r="D42" s="29" t="s">
         <v>141</v>
       </c>
       <c r="E42" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="29" t="s">
-        <v>262</v>
+        <v>150</v>
       </c>
       <c r="G42" s="30">
         <v>30</v>
       </c>
       <c r="H42" s="29" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="I42" s="30">
-        <v>2447</v>
-      </c>
-      <c r="J42" s="15">
-        <f>(9*(100*120*160)+ 4*(100*120*130))/1000000</f>
-        <v>23.52</v>
+        <v>298</v>
+      </c>
+      <c r="J42" s="31">
+        <f>100*120*161/1000000</f>
+        <v>1.9319999999999999</v>
       </c>
       <c r="K42" s="30">
-        <v>6</v>
-      </c>
-      <c r="L42" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M42" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L42" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="M42" s="19" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="18.75" customHeight="1">
       <c r="A43" s="29" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="C43" s="30">
-        <v>14040</v>
+        <v>240</v>
+      </c>
+      <c r="C43" s="29">
+        <v>41019</v>
       </c>
       <c r="D43" s="29" t="s">
         <v>141</v>
@@ -3193,502 +3115,204 @@
         <v>0</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>239</v>
+        <v>150</v>
       </c>
       <c r="G43" s="30">
         <v>30</v>
       </c>
       <c r="H43" s="29" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="I43" s="30">
-        <v>1000</v>
-      </c>
-      <c r="J43" s="15">
-        <f>2.06*2.3*4.6</f>
-        <v>21.794799999999995</v>
-      </c>
-      <c r="K43" s="14">
-        <v>10</v>
-      </c>
-      <c r="L43" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M43" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="J43" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="K43" s="30">
+        <v>2</v>
+      </c>
+      <c r="L43" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="M43" s="19" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="B44" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="30">
-        <v>10040</v>
-      </c>
-      <c r="D44" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E44" s="30">
-        <v>0</v>
-      </c>
-      <c r="F44" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G44" s="30">
-        <v>30</v>
-      </c>
-      <c r="H44" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I44" s="15">
-        <v>6675.74</v>
-      </c>
-      <c r="J44" s="15">
-        <f>(9*(100*120*160)+ 4*(100*120*130))/1000000</f>
-        <v>23.52</v>
-      </c>
-      <c r="K44" s="30">
-        <v>13</v>
-      </c>
-      <c r="L44" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M44" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="34"/>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A45" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="B45" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="C45" s="30">
-        <v>10020</v>
-      </c>
-      <c r="D45" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" s="30">
-        <v>0</v>
-      </c>
-      <c r="F45" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G45" s="30">
-        <v>30</v>
-      </c>
-      <c r="H45" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I45" s="14">
-        <v>486</v>
-      </c>
-      <c r="J45" s="15">
-        <f>100*80*120/1000000</f>
-        <v>0.96</v>
-      </c>
-      <c r="K45" s="30">
-        <v>1</v>
-      </c>
-      <c r="L45" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M45" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A45" s="34"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="34"/>
+      <c r="M45" s="34"/>
     </row>
     <row r="46" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A46" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="B46" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="C46" s="30">
-        <v>15076</v>
-      </c>
-      <c r="D46" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E46" s="30">
-        <v>0</v>
-      </c>
-      <c r="F46" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G46" s="30">
-        <v>30</v>
-      </c>
-      <c r="H46" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I46" s="30">
-        <v>4053</v>
-      </c>
-      <c r="J46" s="31">
-        <v>1.54</v>
-      </c>
-      <c r="K46" s="30">
-        <v>2</v>
-      </c>
-      <c r="L46" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M46" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A46" s="34"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="34"/>
+      <c r="M46" s="34"/>
     </row>
     <row r="47" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A47" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="B47" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="C47" s="30">
-        <v>15011</v>
-      </c>
-      <c r="D47" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E47" s="30">
-        <v>0</v>
-      </c>
-      <c r="F47" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G47" s="30">
-        <v>30</v>
-      </c>
-      <c r="H47" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="I47" s="30">
-        <f>4*600+400</f>
-        <v>2800</v>
-      </c>
-      <c r="J47" s="15">
-        <f>5*100*120*80/1000000</f>
-        <v>4.8</v>
-      </c>
-      <c r="K47" s="30">
-        <v>5</v>
-      </c>
-      <c r="L47" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M47" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A47" s="34"/>
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="34"/>
+      <c r="M47" s="34"/>
     </row>
     <row r="48" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A48" s="29" t="s">
-        <v>248</v>
-      </c>
-      <c r="B48" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="C48" s="30">
-        <v>33043</v>
-      </c>
-      <c r="D48" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E48" s="30">
-        <v>1</v>
-      </c>
-      <c r="F48" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G48" s="30">
-        <v>30</v>
-      </c>
-      <c r="H48" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I48" s="30">
-        <f>4*600+400</f>
-        <v>2800</v>
-      </c>
-      <c r="J48" s="15">
-        <f>5*100*120*80/1000000</f>
-        <v>4.8</v>
-      </c>
-      <c r="K48" s="30">
-        <v>5</v>
-      </c>
-      <c r="L48" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M48" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A48" s="34"/>
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="34"/>
+      <c r="M48" s="34"/>
     </row>
     <row r="49" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A49" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="B49" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="C49" s="30">
-        <v>20044</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E49" s="30">
-        <v>0</v>
-      </c>
-      <c r="F49" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G49" s="30">
-        <v>30</v>
-      </c>
-      <c r="H49" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I49" s="15">
-        <v>6675.74</v>
-      </c>
-      <c r="J49" s="15">
-        <f>(9*(100*120*160)+ 4*(100*120*130))/1000000</f>
-        <v>23.52</v>
-      </c>
-      <c r="K49" s="30">
-        <v>13</v>
-      </c>
-      <c r="L49" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M49" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A49" s="34"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="34"/>
+      <c r="M49" s="34"/>
     </row>
     <row r="50" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A50" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="B50" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="C50" s="30">
-        <v>20143</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E50" s="30">
-        <v>0</v>
-      </c>
-      <c r="F50" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="G50" s="30">
-        <v>30</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I50" s="30">
-        <v>3400</v>
-      </c>
-      <c r="J50" s="15">
-        <f>100*80*120/1000000</f>
-        <v>0.96</v>
-      </c>
-      <c r="K50" s="30">
-        <v>1</v>
-      </c>
-      <c r="L50" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="M50" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A50" s="34"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="34"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="34"/>
+      <c r="M50" s="34"/>
     </row>
     <row r="51" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A51" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="B51" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="C51" s="30">
-        <v>20093</v>
-      </c>
-      <c r="D51" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E51" s="30">
-        <v>0</v>
-      </c>
-      <c r="F51" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G51" s="30">
-        <v>30</v>
-      </c>
-      <c r="H51" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I51" s="30">
-        <v>50640</v>
-      </c>
-      <c r="J51" s="15">
-        <f>3*100*80*120/1000000</f>
-        <v>2.88</v>
-      </c>
-      <c r="K51" s="30">
-        <v>3</v>
-      </c>
-      <c r="L51" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="M51" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A51" s="34"/>
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="34"/>
     </row>
     <row r="52" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A52" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="B52" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="C52" s="30">
-        <v>21050</v>
-      </c>
-      <c r="D52" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E52" s="30">
-        <v>0</v>
-      </c>
-      <c r="F52" s="29" t="s">
-        <v>215</v>
-      </c>
-      <c r="G52" s="30">
-        <v>30</v>
-      </c>
-      <c r="H52" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="I52" s="30">
-        <v>298</v>
-      </c>
-      <c r="J52" s="31">
-        <f>100*120*160/1000000</f>
-        <v>1.92</v>
-      </c>
-      <c r="K52" s="30">
-        <v>1</v>
-      </c>
-      <c r="L52" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="M52" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A52" s="34"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="34"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="33"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="34"/>
+      <c r="M52" s="34"/>
     </row>
     <row r="53" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A53" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="B53" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="C53" s="30">
-        <v>20060</v>
-      </c>
-      <c r="D53" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E53" s="30">
-        <v>1</v>
-      </c>
-      <c r="F53" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G53" s="30">
-        <v>30</v>
-      </c>
-      <c r="H53" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I53" s="30">
-        <v>298</v>
-      </c>
-      <c r="J53" s="31">
-        <f>100*120*161/1000000</f>
-        <v>1.9319999999999999</v>
-      </c>
-      <c r="K53" s="30">
-        <v>1</v>
-      </c>
-      <c r="L53" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="M53" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A53" s="34"/>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="34"/>
+      <c r="M53" s="34"/>
     </row>
     <row r="54" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A54" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="B54" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="C54" s="30">
-        <v>41019</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E54" s="30">
-        <v>0</v>
-      </c>
-      <c r="F54" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="G54" s="30">
-        <v>30</v>
-      </c>
-      <c r="H54" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="I54" s="30">
-        <v>400</v>
-      </c>
-      <c r="J54" s="15">
-        <v>2.5</v>
-      </c>
-      <c r="K54" s="30">
-        <v>2</v>
-      </c>
-      <c r="L54" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="M54" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="A54" s="34"/>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="34"/>
+      <c r="M54" s="34"/>
     </row>
     <row r="55" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A55" s="29"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="29"/>
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="34"/>
       <c r="G55" s="32"/>
-      <c r="H55" s="29"/>
+      <c r="H55" s="34"/>
       <c r="I55" s="32"/>
       <c r="J55" s="33"/>
       <c r="K55" s="32"/>
@@ -3698,7 +3322,7 @@
     <row r="56" spans="1:13" ht="18.75" customHeight="1">
       <c r="A56" s="34"/>
       <c r="B56" s="34"/>
-      <c r="C56" s="32"/>
+      <c r="C56" s="34"/>
       <c r="D56" s="34"/>
       <c r="E56" s="32"/>
       <c r="F56" s="34"/>
@@ -3713,7 +3337,7 @@
     <row r="57" spans="1:13" ht="18.75" customHeight="1">
       <c r="A57" s="34"/>
       <c r="B57" s="34"/>
-      <c r="C57" s="32"/>
+      <c r="C57" s="34"/>
       <c r="D57" s="34"/>
       <c r="E57" s="32"/>
       <c r="F57" s="34"/>
@@ -3728,7 +3352,7 @@
     <row r="58" spans="1:13" ht="18.75" customHeight="1">
       <c r="A58" s="34"/>
       <c r="B58" s="34"/>
-      <c r="C58" s="32"/>
+      <c r="C58" s="34"/>
       <c r="D58" s="34"/>
       <c r="E58" s="32"/>
       <c r="F58" s="34"/>
@@ -3743,7 +3367,7 @@
     <row r="59" spans="1:13" ht="18.75" customHeight="1">
       <c r="A59" s="34"/>
       <c r="B59" s="34"/>
-      <c r="C59" s="32"/>
+      <c r="C59" s="34"/>
       <c r="D59" s="34"/>
       <c r="E59" s="32"/>
       <c r="F59" s="34"/>
@@ -3758,7 +3382,7 @@
     <row r="60" spans="1:13" ht="18.75" customHeight="1">
       <c r="A60" s="34"/>
       <c r="B60" s="34"/>
-      <c r="C60" s="32"/>
+      <c r="C60" s="34"/>
       <c r="D60" s="34"/>
       <c r="E60" s="32"/>
       <c r="F60" s="34"/>
@@ -3773,7 +3397,7 @@
     <row r="61" spans="1:13" ht="18.75" customHeight="1">
       <c r="A61" s="34"/>
       <c r="B61" s="34"/>
-      <c r="C61" s="32"/>
+      <c r="C61" s="34"/>
       <c r="D61" s="34"/>
       <c r="E61" s="32"/>
       <c r="F61" s="34"/>
@@ -3788,7 +3412,7 @@
     <row r="62" spans="1:13" ht="18.75" customHeight="1">
       <c r="A62" s="34"/>
       <c r="B62" s="34"/>
-      <c r="C62" s="32"/>
+      <c r="C62" s="34"/>
       <c r="D62" s="34"/>
       <c r="E62" s="32"/>
       <c r="F62" s="34"/>
@@ -3803,7 +3427,7 @@
     <row r="63" spans="1:13" ht="18.75" customHeight="1">
       <c r="A63" s="34"/>
       <c r="B63" s="34"/>
-      <c r="C63" s="32"/>
+      <c r="C63" s="34"/>
       <c r="D63" s="34"/>
       <c r="E63" s="32"/>
       <c r="F63" s="34"/>
@@ -3818,7 +3442,7 @@
     <row r="64" spans="1:13" ht="18.75" customHeight="1">
       <c r="A64" s="34"/>
       <c r="B64" s="34"/>
-      <c r="C64" s="32"/>
+      <c r="C64" s="34"/>
       <c r="D64" s="34"/>
       <c r="E64" s="32"/>
       <c r="F64" s="34"/>
@@ -3833,7 +3457,7 @@
     <row r="65" spans="1:13" ht="18.75" customHeight="1">
       <c r="A65" s="34"/>
       <c r="B65" s="34"/>
-      <c r="C65" s="32"/>
+      <c r="C65" s="34"/>
       <c r="D65" s="34"/>
       <c r="E65" s="32"/>
       <c r="F65" s="34"/>
@@ -3848,7 +3472,7 @@
     <row r="66" spans="1:13" ht="18.75" customHeight="1">
       <c r="A66" s="34"/>
       <c r="B66" s="34"/>
-      <c r="C66" s="32"/>
+      <c r="C66" s="34"/>
       <c r="D66" s="34"/>
       <c r="E66" s="32"/>
       <c r="F66" s="34"/>
@@ -3863,7 +3487,7 @@
     <row r="67" spans="1:13" ht="18.75" customHeight="1">
       <c r="A67" s="34"/>
       <c r="B67" s="34"/>
-      <c r="C67" s="32"/>
+      <c r="C67" s="34"/>
       <c r="D67" s="34"/>
       <c r="E67" s="32"/>
       <c r="F67" s="34"/>
@@ -3878,7 +3502,7 @@
     <row r="68" spans="1:13" ht="18.75" customHeight="1">
       <c r="A68" s="34"/>
       <c r="B68" s="34"/>
-      <c r="C68" s="32"/>
+      <c r="C68" s="34"/>
       <c r="D68" s="34"/>
       <c r="E68" s="32"/>
       <c r="F68" s="34"/>
@@ -3893,7 +3517,7 @@
     <row r="69" spans="1:13" ht="18.75" customHeight="1">
       <c r="A69" s="34"/>
       <c r="B69" s="34"/>
-      <c r="C69" s="32"/>
+      <c r="C69" s="34"/>
       <c r="D69" s="34"/>
       <c r="E69" s="32"/>
       <c r="F69" s="34"/>
@@ -3908,7 +3532,7 @@
     <row r="70" spans="1:13" ht="18.75" customHeight="1">
       <c r="A70" s="34"/>
       <c r="B70" s="34"/>
-      <c r="C70" s="32"/>
+      <c r="C70" s="34"/>
       <c r="D70" s="34"/>
       <c r="E70" s="32"/>
       <c r="F70" s="34"/>
@@ -3923,7 +3547,7 @@
     <row r="71" spans="1:13" ht="18.75" customHeight="1">
       <c r="A71" s="34"/>
       <c r="B71" s="34"/>
-      <c r="C71" s="32"/>
+      <c r="C71" s="34"/>
       <c r="D71" s="34"/>
       <c r="E71" s="32"/>
       <c r="F71" s="34"/>
@@ -3938,7 +3562,7 @@
     <row r="72" spans="1:13" ht="18.75" customHeight="1">
       <c r="A72" s="34"/>
       <c r="B72" s="34"/>
-      <c r="C72" s="32"/>
+      <c r="C72" s="34"/>
       <c r="D72" s="34"/>
       <c r="E72" s="32"/>
       <c r="F72" s="34"/>
@@ -3953,7 +3577,7 @@
     <row r="73" spans="1:13" ht="18.75" customHeight="1">
       <c r="A73" s="34"/>
       <c r="B73" s="34"/>
-      <c r="C73" s="32"/>
+      <c r="C73" s="34"/>
       <c r="D73" s="34"/>
       <c r="E73" s="32"/>
       <c r="F73" s="34"/>
@@ -3968,7 +3592,7 @@
     <row r="74" spans="1:13" ht="18.75" customHeight="1">
       <c r="A74" s="34"/>
       <c r="B74" s="34"/>
-      <c r="C74" s="32"/>
+      <c r="C74" s="34"/>
       <c r="D74" s="34"/>
       <c r="E74" s="32"/>
       <c r="F74" s="34"/>
@@ -3983,7 +3607,7 @@
     <row r="75" spans="1:13" ht="18.75" customHeight="1">
       <c r="A75" s="34"/>
       <c r="B75" s="34"/>
-      <c r="C75" s="32"/>
+      <c r="C75" s="34"/>
       <c r="D75" s="34"/>
       <c r="E75" s="32"/>
       <c r="F75" s="34"/>
@@ -3998,7 +3622,7 @@
     <row r="76" spans="1:13" ht="18.75" customHeight="1">
       <c r="A76" s="34"/>
       <c r="B76" s="34"/>
-      <c r="C76" s="32"/>
+      <c r="C76" s="34"/>
       <c r="D76" s="34"/>
       <c r="E76" s="32"/>
       <c r="F76" s="34"/>
@@ -4013,7 +3637,7 @@
     <row r="77" spans="1:13" ht="18.75" customHeight="1">
       <c r="A77" s="34"/>
       <c r="B77" s="34"/>
-      <c r="C77" s="32"/>
+      <c r="C77" s="34"/>
       <c r="D77" s="34"/>
       <c r="E77" s="32"/>
       <c r="F77" s="34"/>
@@ -4028,7 +3652,7 @@
     <row r="78" spans="1:13" ht="18.75" customHeight="1">
       <c r="A78" s="34"/>
       <c r="B78" s="34"/>
-      <c r="C78" s="32"/>
+      <c r="C78" s="34"/>
       <c r="D78" s="34"/>
       <c r="E78" s="32"/>
       <c r="F78" s="34"/>
@@ -4043,7 +3667,7 @@
     <row r="79" spans="1:13" ht="18.75" customHeight="1">
       <c r="A79" s="34"/>
       <c r="B79" s="34"/>
-      <c r="C79" s="32"/>
+      <c r="C79" s="34"/>
       <c r="D79" s="34"/>
       <c r="E79" s="32"/>
       <c r="F79" s="34"/>
@@ -4058,7 +3682,7 @@
     <row r="80" spans="1:13" ht="18.75" customHeight="1">
       <c r="A80" s="34"/>
       <c r="B80" s="34"/>
-      <c r="C80" s="32"/>
+      <c r="C80" s="34"/>
       <c r="D80" s="34"/>
       <c r="E80" s="32"/>
       <c r="F80" s="34"/>
@@ -4073,7 +3697,7 @@
     <row r="81" spans="1:13" ht="18.75" customHeight="1">
       <c r="A81" s="34"/>
       <c r="B81" s="34"/>
-      <c r="C81" s="32"/>
+      <c r="C81" s="34"/>
       <c r="D81" s="34"/>
       <c r="E81" s="32"/>
       <c r="F81" s="34"/>
@@ -4088,7 +3712,7 @@
     <row r="82" spans="1:13" ht="18.75" customHeight="1">
       <c r="A82" s="34"/>
       <c r="B82" s="34"/>
-      <c r="C82" s="32"/>
+      <c r="C82" s="34"/>
       <c r="D82" s="34"/>
       <c r="E82" s="32"/>
       <c r="F82" s="34"/>
@@ -4103,7 +3727,7 @@
     <row r="83" spans="1:13" ht="18.75" customHeight="1">
       <c r="A83" s="34"/>
       <c r="B83" s="34"/>
-      <c r="C83" s="32"/>
+      <c r="C83" s="34"/>
       <c r="D83" s="34"/>
       <c r="E83" s="32"/>
       <c r="F83" s="34"/>
@@ -4118,7 +3742,7 @@
     <row r="84" spans="1:13" ht="18.75" customHeight="1">
       <c r="A84" s="34"/>
       <c r="B84" s="34"/>
-      <c r="C84" s="32"/>
+      <c r="C84" s="34"/>
       <c r="D84" s="34"/>
       <c r="E84" s="32"/>
       <c r="F84" s="34"/>
@@ -4133,7 +3757,7 @@
     <row r="85" spans="1:13" ht="18.75" customHeight="1">
       <c r="A85" s="34"/>
       <c r="B85" s="34"/>
-      <c r="C85" s="32"/>
+      <c r="C85" s="34"/>
       <c r="D85" s="34"/>
       <c r="E85" s="32"/>
       <c r="F85" s="34"/>
@@ -4148,7 +3772,7 @@
     <row r="86" spans="1:13" ht="18.75" customHeight="1">
       <c r="A86" s="34"/>
       <c r="B86" s="34"/>
-      <c r="C86" s="32"/>
+      <c r="C86" s="34"/>
       <c r="D86" s="34"/>
       <c r="E86" s="32"/>
       <c r="F86" s="34"/>
@@ -4163,7 +3787,7 @@
     <row r="87" spans="1:13" ht="18.75" customHeight="1">
       <c r="A87" s="34"/>
       <c r="B87" s="34"/>
-      <c r="C87" s="32"/>
+      <c r="C87" s="34"/>
       <c r="D87" s="34"/>
       <c r="E87" s="32"/>
       <c r="F87" s="34"/>
@@ -4178,7 +3802,7 @@
     <row r="88" spans="1:13" ht="18.75" customHeight="1">
       <c r="A88" s="34"/>
       <c r="B88" s="34"/>
-      <c r="C88" s="32"/>
+      <c r="C88" s="34"/>
       <c r="D88" s="34"/>
       <c r="E88" s="32"/>
       <c r="F88" s="34"/>
@@ -4193,7 +3817,7 @@
     <row r="89" spans="1:13" ht="18.75" customHeight="1">
       <c r="A89" s="34"/>
       <c r="B89" s="34"/>
-      <c r="C89" s="32"/>
+      <c r="C89" s="34"/>
       <c r="D89" s="34"/>
       <c r="E89" s="32"/>
       <c r="F89" s="34"/>
@@ -4208,7 +3832,7 @@
     <row r="90" spans="1:13" ht="18.75" customHeight="1">
       <c r="A90" s="34"/>
       <c r="B90" s="34"/>
-      <c r="C90" s="32"/>
+      <c r="C90" s="34"/>
       <c r="D90" s="34"/>
       <c r="E90" s="32"/>
       <c r="F90" s="34"/>
@@ -4223,7 +3847,7 @@
     <row r="91" spans="1:13" ht="18.75" customHeight="1">
       <c r="A91" s="34"/>
       <c r="B91" s="34"/>
-      <c r="C91" s="32"/>
+      <c r="C91" s="34"/>
       <c r="D91" s="34"/>
       <c r="E91" s="32"/>
       <c r="F91" s="34"/>
@@ -4238,7 +3862,7 @@
     <row r="92" spans="1:13" ht="18.75" customHeight="1">
       <c r="A92" s="34"/>
       <c r="B92" s="34"/>
-      <c r="C92" s="32"/>
+      <c r="C92" s="34"/>
       <c r="D92" s="34"/>
       <c r="E92" s="32"/>
       <c r="F92" s="34"/>
@@ -4253,7 +3877,7 @@
     <row r="93" spans="1:13" ht="18.75" customHeight="1">
       <c r="A93" s="34"/>
       <c r="B93" s="34"/>
-      <c r="C93" s="32"/>
+      <c r="C93" s="34"/>
       <c r="D93" s="34"/>
       <c r="E93" s="32"/>
       <c r="F93" s="34"/>
@@ -4268,7 +3892,7 @@
     <row r="94" spans="1:13" ht="18.75" customHeight="1">
       <c r="A94" s="34"/>
       <c r="B94" s="34"/>
-      <c r="C94" s="32"/>
+      <c r="C94" s="34"/>
       <c r="D94" s="34"/>
       <c r="E94" s="32"/>
       <c r="F94" s="34"/>
@@ -4283,7 +3907,7 @@
     <row r="95" spans="1:13" ht="18.75" customHeight="1">
       <c r="A95" s="34"/>
       <c r="B95" s="34"/>
-      <c r="C95" s="32"/>
+      <c r="C95" s="34"/>
       <c r="D95" s="34"/>
       <c r="E95" s="32"/>
       <c r="F95" s="34"/>
@@ -4298,7 +3922,7 @@
     <row r="96" spans="1:13" ht="18.75" customHeight="1">
       <c r="A96" s="34"/>
       <c r="B96" s="34"/>
-      <c r="C96" s="32"/>
+      <c r="C96" s="34"/>
       <c r="D96" s="34"/>
       <c r="E96" s="32"/>
       <c r="F96" s="34"/>
@@ -4313,7 +3937,7 @@
     <row r="97" spans="1:13" ht="18.75" customHeight="1">
       <c r="A97" s="34"/>
       <c r="B97" s="34"/>
-      <c r="C97" s="32"/>
+      <c r="C97" s="34"/>
       <c r="D97" s="34"/>
       <c r="E97" s="32"/>
       <c r="F97" s="34"/>
@@ -4328,7 +3952,7 @@
     <row r="98" spans="1:13" ht="18.75" customHeight="1">
       <c r="A98" s="34"/>
       <c r="B98" s="34"/>
-      <c r="C98" s="32"/>
+      <c r="C98" s="34"/>
       <c r="D98" s="34"/>
       <c r="E98" s="32"/>
       <c r="F98" s="34"/>
@@ -4343,7 +3967,7 @@
     <row r="99" spans="1:13" ht="18.75" customHeight="1">
       <c r="A99" s="34"/>
       <c r="B99" s="34"/>
-      <c r="C99" s="32"/>
+      <c r="C99" s="34"/>
       <c r="D99" s="34"/>
       <c r="E99" s="32"/>
       <c r="F99" s="34"/>
@@ -4358,7 +3982,7 @@
     <row r="100" spans="1:13" ht="18.75" customHeight="1">
       <c r="A100" s="34"/>
       <c r="B100" s="34"/>
-      <c r="C100" s="32"/>
+      <c r="C100" s="34"/>
       <c r="D100" s="34"/>
       <c r="E100" s="32"/>
       <c r="F100" s="34"/>
@@ -4373,7 +3997,7 @@
     <row r="101" spans="1:13" ht="18.75" customHeight="1">
       <c r="A101" s="34"/>
       <c r="B101" s="34"/>
-      <c r="C101" s="32"/>
+      <c r="C101" s="34"/>
       <c r="D101" s="34"/>
       <c r="E101" s="32"/>
       <c r="F101" s="34"/>
@@ -4388,7 +4012,7 @@
     <row r="102" spans="1:13" ht="18.75" customHeight="1">
       <c r="A102" s="34"/>
       <c r="B102" s="34"/>
-      <c r="C102" s="32"/>
+      <c r="C102" s="34"/>
       <c r="D102" s="34"/>
       <c r="E102" s="32"/>
       <c r="F102" s="34"/>
@@ -4403,7 +4027,7 @@
     <row r="103" spans="1:13" ht="18.75" customHeight="1">
       <c r="A103" s="34"/>
       <c r="B103" s="34"/>
-      <c r="C103" s="32"/>
+      <c r="C103" s="34"/>
       <c r="D103" s="34"/>
       <c r="E103" s="32"/>
       <c r="F103" s="34"/>
@@ -4418,7 +4042,7 @@
     <row r="104" spans="1:13" ht="18.75" customHeight="1">
       <c r="A104" s="34"/>
       <c r="B104" s="34"/>
-      <c r="C104" s="32"/>
+      <c r="C104" s="34"/>
       <c r="D104" s="34"/>
       <c r="E104" s="32"/>
       <c r="F104" s="34"/>
@@ -4433,7 +4057,7 @@
     <row r="105" spans="1:13" ht="18.75" customHeight="1">
       <c r="A105" s="34"/>
       <c r="B105" s="34"/>
-      <c r="C105" s="32"/>
+      <c r="C105" s="34"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
       <c r="F105" s="34"/>
@@ -4448,7 +4072,7 @@
     <row r="106" spans="1:13" ht="18.75" customHeight="1">
       <c r="A106" s="34"/>
       <c r="B106" s="34"/>
-      <c r="C106" s="32"/>
+      <c r="C106" s="34"/>
       <c r="D106" s="34"/>
       <c r="E106" s="32"/>
       <c r="F106" s="34"/>
@@ -4463,7 +4087,7 @@
     <row r="107" spans="1:13" ht="18.75" customHeight="1">
       <c r="A107" s="34"/>
       <c r="B107" s="34"/>
-      <c r="C107" s="32"/>
+      <c r="C107" s="34"/>
       <c r="D107" s="34"/>
       <c r="E107" s="32"/>
       <c r="F107" s="34"/>
@@ -4478,7 +4102,7 @@
     <row r="108" spans="1:13" ht="18.75" customHeight="1">
       <c r="A108" s="34"/>
       <c r="B108" s="34"/>
-      <c r="C108" s="32"/>
+      <c r="C108" s="34"/>
       <c r="D108" s="34"/>
       <c r="E108" s="32"/>
       <c r="F108" s="34"/>
@@ -4493,7 +4117,7 @@
     <row r="109" spans="1:13" ht="18.75" customHeight="1">
       <c r="A109" s="34"/>
       <c r="B109" s="34"/>
-      <c r="C109" s="32"/>
+      <c r="C109" s="34"/>
       <c r="D109" s="34"/>
       <c r="E109" s="32"/>
       <c r="F109" s="34"/>
@@ -4508,7 +4132,7 @@
     <row r="110" spans="1:13" ht="18.75" customHeight="1">
       <c r="A110" s="34"/>
       <c r="B110" s="34"/>
-      <c r="C110" s="32"/>
+      <c r="C110" s="34"/>
       <c r="D110" s="34"/>
       <c r="E110" s="32"/>
       <c r="F110" s="34"/>
@@ -4523,7 +4147,7 @@
     <row r="111" spans="1:13" ht="18.75" customHeight="1">
       <c r="A111" s="34"/>
       <c r="B111" s="34"/>
-      <c r="C111" s="32"/>
+      <c r="C111" s="34"/>
       <c r="D111" s="34"/>
       <c r="E111" s="32"/>
       <c r="F111" s="34"/>
@@ -4538,7 +4162,7 @@
     <row r="112" spans="1:13" ht="18.75" customHeight="1">
       <c r="A112" s="34"/>
       <c r="B112" s="34"/>
-      <c r="C112" s="32"/>
+      <c r="C112" s="34"/>
       <c r="D112" s="34"/>
       <c r="E112" s="32"/>
       <c r="F112" s="34"/>
@@ -4553,7 +4177,7 @@
     <row r="113" spans="1:13" ht="18.75" customHeight="1">
       <c r="A113" s="34"/>
       <c r="B113" s="34"/>
-      <c r="C113" s="32"/>
+      <c r="C113" s="34"/>
       <c r="D113" s="34"/>
       <c r="E113" s="32"/>
       <c r="F113" s="34"/>
@@ -4568,7 +4192,7 @@
     <row r="114" spans="1:13" ht="18.75" customHeight="1">
       <c r="A114" s="34"/>
       <c r="B114" s="34"/>
-      <c r="C114" s="32"/>
+      <c r="C114" s="34"/>
       <c r="D114" s="34"/>
       <c r="E114" s="32"/>
       <c r="F114" s="34"/>
@@ -4583,7 +4207,7 @@
     <row r="115" spans="1:13" ht="18.75" customHeight="1">
       <c r="A115" s="34"/>
       <c r="B115" s="34"/>
-      <c r="C115" s="32"/>
+      <c r="C115" s="34"/>
       <c r="D115" s="34"/>
       <c r="E115" s="32"/>
       <c r="F115" s="34"/>
@@ -4598,7 +4222,7 @@
     <row r="116" spans="1:13" ht="18.75" customHeight="1">
       <c r="A116" s="34"/>
       <c r="B116" s="34"/>
-      <c r="C116" s="32"/>
+      <c r="C116" s="34"/>
       <c r="D116" s="34"/>
       <c r="E116" s="32"/>
       <c r="F116" s="34"/>
@@ -4613,7 +4237,7 @@
     <row r="117" spans="1:13" ht="18.75" customHeight="1">
       <c r="A117" s="34"/>
       <c r="B117" s="34"/>
-      <c r="C117" s="32"/>
+      <c r="C117" s="34"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
       <c r="F117" s="34"/>
@@ -4628,7 +4252,7 @@
     <row r="118" spans="1:13" ht="18.75" customHeight="1">
       <c r="A118" s="34"/>
       <c r="B118" s="34"/>
-      <c r="C118" s="32"/>
+      <c r="C118" s="34"/>
       <c r="D118" s="34"/>
       <c r="E118" s="32"/>
       <c r="F118" s="34"/>
@@ -4643,7 +4267,7 @@
     <row r="119" spans="1:13" ht="18.75" customHeight="1">
       <c r="A119" s="34"/>
       <c r="B119" s="34"/>
-      <c r="C119" s="32"/>
+      <c r="C119" s="34"/>
       <c r="D119" s="34"/>
       <c r="E119" s="32"/>
       <c r="F119" s="34"/>
@@ -4658,7 +4282,7 @@
     <row r="120" spans="1:13" ht="18.75" customHeight="1">
       <c r="A120" s="34"/>
       <c r="B120" s="34"/>
-      <c r="C120" s="32"/>
+      <c r="C120" s="34"/>
       <c r="D120" s="34"/>
       <c r="E120" s="32"/>
       <c r="F120" s="34"/>
@@ -4673,7 +4297,7 @@
     <row r="121" spans="1:13" ht="18.75" customHeight="1">
       <c r="A121" s="34"/>
       <c r="B121" s="34"/>
-      <c r="C121" s="32"/>
+      <c r="C121" s="34"/>
       <c r="D121" s="34"/>
       <c r="E121" s="32"/>
       <c r="F121" s="34"/>
@@ -4688,7 +4312,7 @@
     <row r="122" spans="1:13" ht="18.75" customHeight="1">
       <c r="A122" s="34"/>
       <c r="B122" s="34"/>
-      <c r="C122" s="32"/>
+      <c r="C122" s="34"/>
       <c r="D122" s="34"/>
       <c r="E122" s="32"/>
       <c r="F122" s="34"/>
@@ -4703,7 +4327,7 @@
     <row r="123" spans="1:13" ht="18.75" customHeight="1">
       <c r="A123" s="34"/>
       <c r="B123" s="34"/>
-      <c r="C123" s="32"/>
+      <c r="C123" s="34"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
       <c r="F123" s="34"/>
@@ -4718,7 +4342,7 @@
     <row r="124" spans="1:13" ht="18.75" customHeight="1">
       <c r="A124" s="34"/>
       <c r="B124" s="34"/>
-      <c r="C124" s="32"/>
+      <c r="C124" s="34"/>
       <c r="D124" s="34"/>
       <c r="E124" s="32"/>
       <c r="F124" s="34"/>
@@ -4733,7 +4357,7 @@
     <row r="125" spans="1:13" ht="18.75" customHeight="1">
       <c r="A125" s="34"/>
       <c r="B125" s="34"/>
-      <c r="C125" s="32"/>
+      <c r="C125" s="34"/>
       <c r="D125" s="34"/>
       <c r="E125" s="32"/>
       <c r="F125" s="34"/>
@@ -4748,7 +4372,7 @@
     <row r="126" spans="1:13" ht="18.75" customHeight="1">
       <c r="A126" s="34"/>
       <c r="B126" s="34"/>
-      <c r="C126" s="32"/>
+      <c r="C126" s="34"/>
       <c r="D126" s="34"/>
       <c r="E126" s="32"/>
       <c r="F126" s="34"/>
@@ -4763,7 +4387,7 @@
     <row r="127" spans="1:13" ht="18.75" customHeight="1">
       <c r="A127" s="34"/>
       <c r="B127" s="34"/>
-      <c r="C127" s="32"/>
+      <c r="C127" s="34"/>
       <c r="D127" s="34"/>
       <c r="E127" s="32"/>
       <c r="F127" s="34"/>
@@ -4778,7 +4402,7 @@
     <row r="128" spans="1:13" ht="18.75" customHeight="1">
       <c r="A128" s="34"/>
       <c r="B128" s="34"/>
-      <c r="C128" s="32"/>
+      <c r="C128" s="34"/>
       <c r="D128" s="34"/>
       <c r="E128" s="32"/>
       <c r="F128" s="34"/>
@@ -4793,7 +4417,7 @@
     <row r="129" spans="1:13" ht="18.75" customHeight="1">
       <c r="A129" s="34"/>
       <c r="B129" s="34"/>
-      <c r="C129" s="32"/>
+      <c r="C129" s="34"/>
       <c r="D129" s="34"/>
       <c r="E129" s="32"/>
       <c r="F129" s="34"/>
@@ -4808,7 +4432,7 @@
     <row r="130" spans="1:13" ht="18.75" customHeight="1">
       <c r="A130" s="34"/>
       <c r="B130" s="34"/>
-      <c r="C130" s="32"/>
+      <c r="C130" s="34"/>
       <c r="D130" s="34"/>
       <c r="E130" s="32"/>
       <c r="F130" s="34"/>
@@ -4823,7 +4447,7 @@
     <row r="131" spans="1:13" ht="18.75" customHeight="1">
       <c r="A131" s="34"/>
       <c r="B131" s="34"/>
-      <c r="C131" s="32"/>
+      <c r="C131" s="34"/>
       <c r="D131" s="34"/>
       <c r="E131" s="32"/>
       <c r="F131" s="34"/>
@@ -4838,7 +4462,7 @@
     <row r="132" spans="1:13" ht="18.75" customHeight="1">
       <c r="A132" s="34"/>
       <c r="B132" s="34"/>
-      <c r="C132" s="32"/>
+      <c r="C132" s="34"/>
       <c r="D132" s="34"/>
       <c r="E132" s="32"/>
       <c r="F132" s="34"/>
@@ -4853,7 +4477,7 @@
     <row r="133" spans="1:13" ht="18.75" customHeight="1">
       <c r="A133" s="34"/>
       <c r="B133" s="34"/>
-      <c r="C133" s="32"/>
+      <c r="C133" s="34"/>
       <c r="D133" s="34"/>
       <c r="E133" s="32"/>
       <c r="F133" s="34"/>
@@ -4868,7 +4492,7 @@
     <row r="134" spans="1:13" ht="18.75" customHeight="1">
       <c r="A134" s="34"/>
       <c r="B134" s="34"/>
-      <c r="C134" s="32"/>
+      <c r="C134" s="34"/>
       <c r="D134" s="34"/>
       <c r="E134" s="32"/>
       <c r="F134" s="34"/>
@@ -4883,7 +4507,7 @@
     <row r="135" spans="1:13" ht="18.75" customHeight="1">
       <c r="A135" s="34"/>
       <c r="B135" s="34"/>
-      <c r="C135" s="32"/>
+      <c r="C135" s="34"/>
       <c r="D135" s="34"/>
       <c r="E135" s="32"/>
       <c r="F135" s="34"/>
@@ -4894,171 +4518,6 @@
       <c r="K135" s="32"/>
       <c r="L135" s="34"/>
       <c r="M135" s="34"/>
-    </row>
-    <row r="136" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A136" s="34"/>
-      <c r="B136" s="34"/>
-      <c r="C136" s="32"/>
-      <c r="D136" s="34"/>
-      <c r="E136" s="32"/>
-      <c r="F136" s="34"/>
-      <c r="G136" s="32"/>
-      <c r="H136" s="34"/>
-      <c r="I136" s="32"/>
-      <c r="J136" s="33"/>
-      <c r="K136" s="32"/>
-      <c r="L136" s="34"/>
-      <c r="M136" s="34"/>
-    </row>
-    <row r="137" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A137" s="34"/>
-      <c r="B137" s="34"/>
-      <c r="C137" s="32"/>
-      <c r="D137" s="34"/>
-      <c r="E137" s="32"/>
-      <c r="F137" s="34"/>
-      <c r="G137" s="32"/>
-      <c r="H137" s="34"/>
-      <c r="I137" s="32"/>
-      <c r="J137" s="33"/>
-      <c r="K137" s="32"/>
-      <c r="L137" s="34"/>
-      <c r="M137" s="34"/>
-    </row>
-    <row r="138" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A138" s="34"/>
-      <c r="B138" s="34"/>
-      <c r="C138" s="32"/>
-      <c r="D138" s="34"/>
-      <c r="E138" s="32"/>
-      <c r="F138" s="34"/>
-      <c r="G138" s="32"/>
-      <c r="H138" s="34"/>
-      <c r="I138" s="32"/>
-      <c r="J138" s="33"/>
-      <c r="K138" s="32"/>
-      <c r="L138" s="34"/>
-      <c r="M138" s="34"/>
-    </row>
-    <row r="139" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A139" s="34"/>
-      <c r="B139" s="34"/>
-      <c r="C139" s="32"/>
-      <c r="D139" s="34"/>
-      <c r="E139" s="32"/>
-      <c r="F139" s="34"/>
-      <c r="G139" s="32"/>
-      <c r="H139" s="34"/>
-      <c r="I139" s="32"/>
-      <c r="J139" s="33"/>
-      <c r="K139" s="32"/>
-      <c r="L139" s="34"/>
-      <c r="M139" s="34"/>
-    </row>
-    <row r="140" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A140" s="34"/>
-      <c r="B140" s="34"/>
-      <c r="C140" s="32"/>
-      <c r="D140" s="34"/>
-      <c r="E140" s="32"/>
-      <c r="F140" s="34"/>
-      <c r="G140" s="32"/>
-      <c r="H140" s="34"/>
-      <c r="I140" s="32"/>
-      <c r="J140" s="33"/>
-      <c r="K140" s="32"/>
-      <c r="L140" s="34"/>
-      <c r="M140" s="34"/>
-    </row>
-    <row r="141" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A141" s="34"/>
-      <c r="B141" s="34"/>
-      <c r="C141" s="32"/>
-      <c r="D141" s="34"/>
-      <c r="E141" s="32"/>
-      <c r="F141" s="34"/>
-      <c r="G141" s="32"/>
-      <c r="H141" s="34"/>
-      <c r="I141" s="32"/>
-      <c r="J141" s="33"/>
-      <c r="K141" s="32"/>
-      <c r="L141" s="34"/>
-      <c r="M141" s="34"/>
-    </row>
-    <row r="142" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A142" s="34"/>
-      <c r="B142" s="34"/>
-      <c r="C142" s="32"/>
-      <c r="D142" s="34"/>
-      <c r="E142" s="32"/>
-      <c r="F142" s="34"/>
-      <c r="G142" s="32"/>
-      <c r="H142" s="34"/>
-      <c r="I142" s="32"/>
-      <c r="J142" s="33"/>
-      <c r="K142" s="32"/>
-      <c r="L142" s="34"/>
-      <c r="M142" s="34"/>
-    </row>
-    <row r="143" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A143" s="34"/>
-      <c r="B143" s="34"/>
-      <c r="C143" s="32"/>
-      <c r="D143" s="34"/>
-      <c r="E143" s="32"/>
-      <c r="F143" s="34"/>
-      <c r="G143" s="32"/>
-      <c r="H143" s="34"/>
-      <c r="I143" s="32"/>
-      <c r="J143" s="33"/>
-      <c r="K143" s="32"/>
-      <c r="L143" s="34"/>
-      <c r="M143" s="34"/>
-    </row>
-    <row r="144" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A144" s="34"/>
-      <c r="B144" s="34"/>
-      <c r="C144" s="32"/>
-      <c r="D144" s="34"/>
-      <c r="E144" s="32"/>
-      <c r="F144" s="34"/>
-      <c r="G144" s="32"/>
-      <c r="H144" s="34"/>
-      <c r="I144" s="32"/>
-      <c r="J144" s="33"/>
-      <c r="K144" s="32"/>
-      <c r="L144" s="34"/>
-      <c r="M144" s="34"/>
-    </row>
-    <row r="145" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A145" s="34"/>
-      <c r="B145" s="34"/>
-      <c r="C145" s="32"/>
-      <c r="D145" s="34"/>
-      <c r="E145" s="32"/>
-      <c r="F145" s="34"/>
-      <c r="G145" s="32"/>
-      <c r="H145" s="34"/>
-      <c r="I145" s="32"/>
-      <c r="J145" s="33"/>
-      <c r="K145" s="32"/>
-      <c r="L145" s="34"/>
-      <c r="M145" s="34"/>
-    </row>
-    <row r="146" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A146" s="34"/>
-      <c r="B146" s="34"/>
-      <c r="C146" s="32"/>
-      <c r="D146" s="34"/>
-      <c r="E146" s="32"/>
-      <c r="F146" s="34"/>
-      <c r="G146" s="32"/>
-      <c r="H146" s="34"/>
-      <c r="I146" s="32"/>
-      <c r="J146" s="33"/>
-      <c r="K146" s="32"/>
-      <c r="L146" s="34"/>
-      <c r="M146" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5073,17 +4532,17 @@
   <dimension ref="A1:O56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.5703125" style="26" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5094,13 +4553,13 @@
       <c r="B1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>119</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -5109,7 +4568,7 @@
       <c r="G1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>122</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -5128,1925 +4587,1925 @@
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="15">
         <v>800</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="15">
         <v>9</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="16">
         <f>2.06*2.3*4.6</f>
         <v>21.794799999999995</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
+      <c r="F2" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
     </row>
     <row r="3" spans="1:15" ht="18.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="15">
         <v>13500</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="15">
         <v>23</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="21">
         <f>2.48*2.82*9.6</f>
         <v>67.138559999999998</v>
       </c>
-      <c r="F3" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
+      <c r="F3" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
     </row>
     <row r="4" spans="1:15" ht="18.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="15">
         <v>700</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="15">
         <v>8</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="16">
         <f>2.06*2.1*4.2</f>
         <v>18.169200000000004</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
+      <c r="F4" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
     </row>
     <row r="5" spans="1:15" ht="18.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="15">
         <v>8000</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="15">
         <v>20</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="21">
         <f>2.48*2.8*8.2</f>
         <v>56.940799999999996</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
+      <c r="F5" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
     </row>
     <row r="6" spans="1:15" ht="18.75" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="15">
         <v>800</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="15">
         <v>4</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="16">
         <f>1.55*1.65*3.2</f>
         <v>8.1840000000000011</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
+      <c r="F6" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
     </row>
     <row r="7" spans="1:15" ht="18.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="15">
         <v>700</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="15">
         <v>8</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="16">
         <f>2.06*2.1*4.2</f>
         <v>18.169200000000004</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
+      <c r="F7" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="15">
         <v>700</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <v>10</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="16">
         <f>2.06*2.4*4.98</f>
         <v>24.621120000000001</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
+      <c r="F8" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" spans="1:15" ht="18.75" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="15">
         <v>800</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="15">
         <v>6</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="16">
         <f>1.6*1.8*4.7</f>
         <v>13.536000000000001</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
+      <c r="F9" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
     </row>
     <row r="10" spans="1:15" ht="18.75" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="15">
         <v>800</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="15">
         <v>6</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="16">
         <v>13.536000000000001</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
+      <c r="F10" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
     </row>
     <row r="11" spans="1:15" ht="18.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="15">
         <v>700</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="15">
         <v>10</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="16">
         <f>2.06*2.4*4.98</f>
         <v>24.621120000000001</v>
       </c>
-      <c r="F11" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
+      <c r="F11" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
     </row>
     <row r="12" spans="1:15" ht="18.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="15">
         <v>2100</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="15">
         <v>16</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>2.48*2.8*6.6</f>
         <v>45.830399999999997</v>
       </c>
-      <c r="F12" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
+      <c r="F12" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:15" ht="18.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="15">
         <v>5000</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="15">
         <v>18</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>2.48*2.8*7.6</f>
         <v>52.7744</v>
       </c>
-      <c r="F13" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
+      <c r="F13" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
     </row>
     <row r="14" spans="1:15" ht="18.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="15">
         <v>700</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="15">
         <v>10</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="16">
         <f>2.06*2.4*4.98</f>
         <v>24.621120000000001</v>
       </c>
-      <c r="F14" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
+      <c r="F14" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
     </row>
     <row r="15" spans="1:15" ht="18.75" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="15">
         <v>2100</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="15">
         <v>16</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <f>2.48*2.8*6.7</f>
         <v>46.524799999999999</v>
       </c>
-      <c r="F15" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
+      <c r="F15" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
     </row>
     <row r="16" spans="1:15" ht="18.75" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="15">
         <v>8000</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="15">
         <v>18</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>2.48*2.8*7.7</f>
         <v>53.468800000000002</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
+      <c r="F16" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
     </row>
     <row r="17" spans="1:12" ht="18.75" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="15">
         <v>900</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="15">
         <v>5</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="16">
         <f>1.6*1.8*4.3</f>
         <v>12.384</v>
       </c>
-      <c r="F17" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
+      <c r="F17" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
     </row>
     <row r="18" spans="1:12" ht="18.75" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="15">
         <v>800</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="15">
         <v>6</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="16">
         <f>1.6*1.8*4.7</f>
         <v>13.536000000000001</v>
       </c>
-      <c r="F18" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
+      <c r="F18" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
     </row>
     <row r="19" spans="1:12" ht="18.75" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="15">
         <v>8500</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="15">
         <v>19</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="21">
         <f>2.48*2.8*7.9</f>
         <v>54.857600000000005</v>
       </c>
-      <c r="F19" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
+      <c r="F19" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
     </row>
     <row r="20" spans="1:12" ht="18.75" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="15">
         <v>800</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="15">
         <v>6</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="16">
         <f>1.6*1.8*4.7</f>
         <v>13.536000000000001</v>
       </c>
-      <c r="F20" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
+      <c r="F20" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
     </row>
     <row r="21" spans="1:12" ht="18.75" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="15">
         <v>700</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="15">
         <v>10</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="16">
         <f>2.06*2.4*4.98</f>
         <v>24.621120000000001</v>
       </c>
-      <c r="F21" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
+      <c r="F21" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="15">
         <v>800</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="15">
         <v>9</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="21">
         <f>2.2*2.8*4.6</f>
         <v>28.335999999999999</v>
       </c>
-      <c r="F22" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
+      <c r="F22" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="15">
         <v>700</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="15">
         <v>9</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="16">
         <f>2.06*2.3*4.6</f>
         <v>21.794799999999995</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
+      <c r="F23" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="15">
         <v>13500</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="15">
         <v>23</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="21">
         <f>2.48*2.8*9.6</f>
         <v>66.662399999999991</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
+      <c r="F24" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="15">
         <v>800</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="15">
         <v>6</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="16">
         <f>1.6*1.8*4.7</f>
         <v>13.536000000000001</v>
       </c>
-      <c r="F25" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
+      <c r="F25" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
     </row>
     <row r="26" spans="1:12" ht="18.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="15">
         <v>700</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="15">
         <v>6</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="16">
         <f>2.06*2.1*3.2</f>
         <v>13.843200000000003</v>
       </c>
-      <c r="F26" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
+      <c r="F26" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="15">
         <v>700</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="15">
         <v>10</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="21">
         <f>2.2*2.8*4.97</f>
         <v>30.615199999999998</v>
       </c>
-      <c r="F27" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I27" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
+      <c r="F27" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
     </row>
     <row r="28" spans="1:12" ht="18.75" customHeight="1">
       <c r="A28" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="15">
         <v>44000</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="15">
         <v>38</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="16">
         <f>2.8*2.48*(7.7+7.7)</f>
         <v>106.9376</v>
       </c>
-      <c r="F28" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
+      <c r="F28" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
     </row>
     <row r="29" spans="1:12" ht="18.75" customHeight="1">
       <c r="A29" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="15">
         <v>1000</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="15">
         <v>4</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="16">
         <f>1.6*1.8*3.2</f>
         <v>9.2160000000000011</v>
       </c>
-      <c r="F29" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I29" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J29" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
+      <c r="F29" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
     </row>
     <row r="30" spans="1:12" ht="18.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="15">
         <v>700</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="15">
         <v>10</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="16">
         <f>2.06*2.4*4.98</f>
         <v>24.621120000000001</v>
       </c>
-      <c r="F30" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I30" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J30" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
+      <c r="F30" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="15">
         <v>8000</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="15">
         <v>20</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="21">
         <f>2.48*2.8*8.2</f>
         <v>56.940799999999996</v>
       </c>
-      <c r="F31" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G31" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I31" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J31" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
+      <c r="F31" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="15">
         <v>700</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="15">
         <v>10</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="16">
         <f>2.06*2.4*4.98</f>
         <v>24.621120000000001</v>
       </c>
-      <c r="F32" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I32" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
+      <c r="F32" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="15">
         <v>700</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="15">
         <v>10</v>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="21">
         <f>2.2*2.8*4.97</f>
         <v>30.615199999999998</v>
       </c>
-      <c r="F33" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G33" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H33" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I33" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
+      <c r="F33" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I33" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="15">
         <v>700</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="15">
         <v>10</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="21">
         <f>2.2*2.8*4.97</f>
         <v>30.615199999999998</v>
       </c>
-      <c r="F34" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I34" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
+      <c r="F34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="15">
         <v>700</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="15">
         <v>10</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="21">
         <f>2.2*2.8*4.97</f>
         <v>30.615199999999998</v>
       </c>
-      <c r="F35" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G35" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H35" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I35" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J35" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
+      <c r="F35" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I35" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="15">
         <v>800</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="15">
         <v>9</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="16">
         <f>2.04*2.3*4.6</f>
         <v>21.583199999999994</v>
       </c>
-      <c r="F36" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I36" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J36" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
+      <c r="F36" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="15">
         <v>700</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="15">
         <v>8</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="16">
         <f>2.06*2.1*4.2</f>
         <v>18.169200000000004</v>
       </c>
-      <c r="F37" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I37" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J37" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
+      <c r="F37" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H37" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J37" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
     </row>
     <row r="38" spans="1:12" ht="18.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="15">
         <v>700</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="15">
         <v>10</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="21">
         <f>2.2*2.8*4.97</f>
         <v>30.615199999999998</v>
       </c>
-      <c r="F38" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G38" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H38" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I38" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J38" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
+      <c r="F38" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I38" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
     </row>
     <row r="39" spans="1:12" ht="18.75" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="15">
         <v>700</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="15">
         <v>10</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="21">
         <f>2.2*2.8*4.97</f>
         <v>30.615199999999998</v>
       </c>
-      <c r="F39" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G39" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H39" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I39" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J39" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
+      <c r="F39" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
     </row>
     <row r="40" spans="1:12" ht="18.75" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="15">
         <v>700</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="15">
         <v>10</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="16">
         <f>2.06*2.4*4.98</f>
         <v>24.621120000000001</v>
       </c>
-      <c r="F40" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I40" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J40" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
+      <c r="F40" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="15">
         <v>700</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D41" s="15">
         <v>8</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="16">
         <f>2.06*2.1*4.2</f>
         <v>18.169200000000004</v>
       </c>
-      <c r="F41" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G41" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H41" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I41" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J41" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
+      <c r="F41" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H41" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J41" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" customHeight="1">
       <c r="A42" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="15">
         <v>700</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="15">
         <v>10</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="16">
         <f>2.06*2.4*4.98</f>
         <v>24.621120000000001</v>
       </c>
-      <c r="F42" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H42" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I42" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J42" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
+      <c r="F42" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J42" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
     </row>
     <row r="43" spans="1:12" ht="18.75" customHeight="1">
       <c r="A43" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="15">
         <v>700</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D43" s="15">
         <v>8</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="16">
         <f>2.06*2.1*4.2</f>
         <v>18.169200000000004</v>
       </c>
-      <c r="F43" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G43" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I43" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J43" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
+      <c r="F43" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J43" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="15">
         <v>700</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="15">
         <v>10</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="24">
         <f>2.2*2.8*4.97</f>
         <v>30.615199999999998</v>
       </c>
-      <c r="F44" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G44" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H44" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I44" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J44" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
+      <c r="F44" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J44" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
     </row>
     <row r="45" spans="1:12" ht="18.75" customHeight="1">
       <c r="A45" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="15">
         <v>800</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D45" s="15">
         <v>4</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="16">
         <f>1.55*1.65*3.2</f>
         <v>8.1840000000000011</v>
       </c>
-      <c r="F45" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G45" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H45" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I45" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J45" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
+      <c r="F45" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I45" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J45" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
     </row>
     <row r="46" spans="1:12" ht="18.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C46" s="14">
+      <c r="C46" s="15">
         <v>700</v>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="15">
         <v>10</v>
       </c>
-      <c r="E46" s="15">
+      <c r="E46" s="16">
         <f>2.06*2.4*4.98</f>
         <v>24.621120000000001</v>
       </c>
-      <c r="F46" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G46" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H46" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I46" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J46" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K46" s="18"/>
-      <c r="L46" s="18"/>
+      <c r="F46" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G46" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H46" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I46" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J46" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19"/>
     </row>
     <row r="47" spans="1:12" ht="18.75" customHeight="1">
       <c r="A47" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="15">
         <v>700</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="15">
         <v>10</v>
       </c>
-      <c r="E47" s="20">
+      <c r="E47" s="21">
         <f>2.2*2.8*4.97</f>
         <v>30.615199999999998</v>
       </c>
-      <c r="F47" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G47" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H47" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I47" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J47" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K47" s="18"/>
-      <c r="L47" s="18"/>
+      <c r="F47" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I47" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J47" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K47" s="19"/>
+      <c r="L47" s="19"/>
     </row>
     <row r="48" spans="1:12" ht="18.75" customHeight="1">
       <c r="A48" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C48" s="14">
+      <c r="C48" s="15">
         <v>700</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="15">
         <v>10</v>
       </c>
-      <c r="E48" s="20">
+      <c r="E48" s="21">
         <f>2.2*2.8*4.97</f>
         <v>30.615199999999998</v>
       </c>
-      <c r="F48" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G48" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H48" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I48" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J48" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
+      <c r="F48" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I48" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J48" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
     </row>
     <row r="49" spans="1:12" ht="18.75" customHeight="1">
       <c r="A49" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="15">
         <v>800</v>
       </c>
-      <c r="D49" s="14">
+      <c r="D49" s="15">
         <v>9</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E49" s="21">
         <f>2.2*2.8*4.6</f>
         <v>28.335999999999999</v>
       </c>
-      <c r="F49" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H49" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I49" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J49" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
+      <c r="F49" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I49" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J49" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
     </row>
     <row r="50" spans="1:12" ht="18.75" customHeight="1">
       <c r="A50" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="15">
         <v>600</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="15">
         <v>9</v>
       </c>
-      <c r="E50" s="15">
+      <c r="E50" s="16">
         <f>2.06*2.1*4.6</f>
         <v>19.8996</v>
       </c>
-      <c r="F50" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G50" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H50" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I50" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J50" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K50" s="18"/>
-      <c r="L50" s="18"/>
+      <c r="F50" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G50" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I50" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J50" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K50" s="19"/>
+      <c r="L50" s="19"/>
     </row>
     <row r="51" spans="1:12" ht="18.75" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="15">
         <v>32700</v>
       </c>
-      <c r="D51" s="14">
+      <c r="D51" s="15">
         <v>33</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="16">
         <f>2.48*2.7*13.6</f>
         <v>91.065600000000003</v>
       </c>
-      <c r="F51" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G51" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H51" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I51" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J51" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K51" s="18"/>
-      <c r="L51" s="18"/>
+      <c r="F51" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H51" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I51" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J51" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K51" s="19"/>
+      <c r="L51" s="19"/>
     </row>
     <row r="52" spans="1:12" ht="18.75" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B52" s="24" t="s">
+      <c r="B52" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="14">
+      <c r="C52" s="15">
         <v>32000</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="15">
         <v>33</v>
       </c>
-      <c r="E52" s="15">
+      <c r="E52" s="16">
         <f>2.48*2.7*13.6</f>
         <v>91.065600000000003</v>
       </c>
-      <c r="F52" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H52" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I52" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J52" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
+      <c r="F52" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I52" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J52" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
     </row>
     <row r="53" spans="1:12" ht="18.75" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="24" t="s">
+      <c r="B53" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C53" s="14">
+      <c r="C53" s="15">
         <v>32700</v>
       </c>
-      <c r="D53" s="14">
+      <c r="D53" s="15">
         <v>33</v>
       </c>
-      <c r="E53" s="15">
+      <c r="E53" s="16">
         <f>2.48*2.6*13.6</f>
         <v>87.692800000000005</v>
       </c>
-      <c r="F53" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G53" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H53" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I53" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J53" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
+      <c r="F53" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G53" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H53" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I53" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J53" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K53" s="19"/>
+      <c r="L53" s="19"/>
     </row>
     <row r="54" spans="1:12" ht="18.75" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="24" t="s">
+      <c r="B54" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C54" s="14">
+      <c r="C54" s="15">
         <v>32700</v>
       </c>
-      <c r="D54" s="14">
+      <c r="D54" s="15">
         <v>33</v>
       </c>
-      <c r="E54" s="15">
+      <c r="E54" s="16">
         <f>2.48*2.7*13.6</f>
         <v>91.065600000000003</v>
       </c>
-      <c r="F54" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H54" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I54" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J54" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
+      <c r="F54" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G54" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H54" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I54" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J54" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K54" s="19"/>
+      <c r="L54" s="19"/>
     </row>
     <row r="55" spans="1:12" ht="18.75" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="15">
         <v>24300</v>
       </c>
-      <c r="D55" s="14">
+      <c r="D55" s="15">
         <v>27</v>
       </c>
-      <c r="E55" s="15">
+      <c r="E55" s="16">
         <f>2.48*2.7*11</f>
         <v>73.656000000000006</v>
       </c>
-      <c r="F55" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H55" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I55" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J55" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
+      <c r="F55" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H55" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I55" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J55" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K55" s="19"/>
+      <c r="L55" s="19"/>
     </row>
     <row r="56" spans="1:12" ht="18.75" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B56" s="24" t="s">
+      <c r="B56" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C56" s="14">
+      <c r="C56" s="15">
         <v>32700</v>
       </c>
-      <c r="D56" s="14">
+      <c r="D56" s="15">
         <v>33</v>
       </c>
-      <c r="E56" s="15">
+      <c r="E56" s="16">
         <f>2.48*2.7*13.6</f>
         <v>91.065600000000003</v>
       </c>
-      <c r="F56" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G56" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H56" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I56" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="J56" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K56" s="18"/>
-      <c r="L56" s="18"/>
+      <c r="F56" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H56" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I56" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J56" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K56" s="19"/>
+      <c r="L56" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7061,7 +6520,7 @@
   <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -7693,10 +7152,10 @@
     <row r="65" spans="1:1" ht="18.75" customHeight="1"/>
     <row r="66" spans="1:1" ht="18.75" customHeight="1"/>
     <row r="67" spans="1:1" ht="18.75" customHeight="1">
-      <c r="A67" s="8"/>
+      <c r="A67" s="9"/>
     </row>
     <row r="68" spans="1:1" ht="18.75" customHeight="1">
-      <c r="A68" s="9"/>
+      <c r="A68" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
